--- a/src/attributions/attributions_saliency_traj_127.xlsx
+++ b/src/attributions/attributions_saliency_traj_127.xlsx
@@ -1568,1140 +1568,1140 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>0.2281805723905563</v>
+        <v>0.03863083943724632</v>
       </c>
       <c r="B3" t="n">
-        <v>1.903566241264343</v>
+        <v>0.7965762615203857</v>
       </c>
       <c r="C3" t="n">
-        <v>0.192891001701355</v>
+        <v>0.1133497804403305</v>
       </c>
       <c r="D3" t="n">
-        <v>0.1732074618339539</v>
+        <v>0.1696687042713165</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1543260812759399</v>
+        <v>0.0009918585419654846</v>
       </c>
       <c r="F3" t="n">
-        <v>1.575911521911621</v>
+        <v>0.1985655575990677</v>
       </c>
       <c r="G3" t="n">
-        <v>0.1373493373394012</v>
+        <v>0.05730356276035309</v>
       </c>
       <c r="H3" t="n">
-        <v>0.7364307045936584</v>
+        <v>0.1973113417625427</v>
       </c>
       <c r="I3" t="n">
-        <v>0.2121966481208801</v>
+        <v>0.006503332406282425</v>
       </c>
       <c r="J3" t="n">
-        <v>0.5498256683349609</v>
+        <v>0.06912660598754883</v>
       </c>
       <c r="K3" t="n">
-        <v>1.760661482810974</v>
+        <v>0.8283659219741821</v>
       </c>
       <c r="L3" t="n">
-        <v>0.2195669412612915</v>
+        <v>0.1611387878656387</v>
       </c>
       <c r="M3" t="n">
-        <v>0.1400458514690399</v>
+        <v>0.2345573902130127</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5157753229141235</v>
+        <v>0.116871289908886</v>
       </c>
       <c r="O3" t="n">
-        <v>0.8945491313934326</v>
+        <v>0.0846003070473671</v>
       </c>
       <c r="P3" t="n">
-        <v>0.08319921791553497</v>
+        <v>0.07991643249988556</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.3747981786727905</v>
+        <v>0.2129662036895752</v>
       </c>
       <c r="R3" t="n">
-        <v>0.03632771223783493</v>
+        <v>0.08172544836997986</v>
       </c>
       <c r="S3" t="n">
-        <v>0.286093145608902</v>
+        <v>0.09599429368972778</v>
       </c>
       <c r="T3" t="n">
-        <v>0.04947400093078613</v>
+        <v>0.1592320948839188</v>
       </c>
       <c r="U3" t="n">
-        <v>0.2122914046049118</v>
+        <v>0.06244755536317825</v>
       </c>
       <c r="V3" t="n">
-        <v>0.1946179270744324</v>
+        <v>0.007709097117185593</v>
       </c>
       <c r="W3" t="n">
-        <v>0.5291500091552734</v>
+        <v>0.03397758677601814</v>
       </c>
       <c r="X3" t="n">
-        <v>0.07804866135120392</v>
+        <v>0.05873456597328186</v>
       </c>
       <c r="Y3" t="n">
-        <v>0.01742229983210564</v>
+        <v>0.07573563605546951</v>
       </c>
       <c r="Z3" t="n">
-        <v>0.02876785397529602</v>
+        <v>0.04105880856513977</v>
       </c>
       <c r="AA3" t="n">
-        <v>0.1220944225788116</v>
+        <v>0.0063978536054492</v>
       </c>
       <c r="AB3" t="n">
-        <v>0.15456622838974</v>
+        <v>0.04000616446137428</v>
       </c>
       <c r="AC3" t="n">
-        <v>0.02994547411799431</v>
+        <v>0.05652303621172905</v>
       </c>
       <c r="AD3" t="n">
-        <v>0.05771945416927338</v>
+        <v>0.07297994196414948</v>
       </c>
       <c r="AE3" t="n">
-        <v>0.05270197242498398</v>
+        <v>0.1892973780632019</v>
       </c>
       <c r="AF3" t="n">
-        <v>0.138932853937149</v>
+        <v>0.04537273570895195</v>
       </c>
       <c r="AG3" t="n">
-        <v>0.1135761439800262</v>
+        <v>0.06424172967672348</v>
       </c>
       <c r="AH3" t="n">
-        <v>0.09166404604911804</v>
+        <v>0.02929562702775002</v>
       </c>
       <c r="AI3" t="n">
-        <v>0.06434321403503418</v>
+        <v>0.090920589864254</v>
       </c>
       <c r="AJ3" t="n">
-        <v>0.07585447281599045</v>
+        <v>0.01060459669679403</v>
       </c>
       <c r="AK3" t="n">
-        <v>0.3673413097858429</v>
+        <v>0.007481604814529419</v>
       </c>
       <c r="AL3" t="n">
-        <v>0.06325297057628632</v>
+        <v>0.1851922869682312</v>
       </c>
       <c r="AM3" t="n">
-        <v>0.08744345605373383</v>
+        <v>0.07685918360948563</v>
       </c>
       <c r="AN3" t="n">
-        <v>0.211085170507431</v>
+        <v>0.02905328571796417</v>
       </c>
       <c r="AO3" t="n">
-        <v>0.1267871558666229</v>
+        <v>0.1747369319200516</v>
       </c>
       <c r="AP3" t="n">
-        <v>0.5449624061584473</v>
+        <v>0.04976950585842133</v>
       </c>
       <c r="AQ3" t="n">
-        <v>0.02497466467320919</v>
+        <v>0.09626399725675583</v>
       </c>
       <c r="AR3" t="n">
-        <v>0.1658990085124969</v>
+        <v>0.02808650583028793</v>
       </c>
       <c r="AS3" t="n">
-        <v>0.05234215408563614</v>
+        <v>0.04296493902802467</v>
       </c>
       <c r="AT3" t="n">
-        <v>0.2343023717403412</v>
+        <v>0.1052761450409889</v>
       </c>
       <c r="AU3" t="n">
-        <v>0.9154345393180847</v>
+        <v>0.463993638753891</v>
       </c>
       <c r="AV3" t="n">
-        <v>0.3727997541427612</v>
+        <v>0.02748673595488071</v>
       </c>
       <c r="AW3" t="n">
-        <v>0.03835147619247437</v>
+        <v>0.002062694169580936</v>
       </c>
       <c r="AX3" t="n">
-        <v>0.2390615493059158</v>
+        <v>0.001730488147586584</v>
       </c>
       <c r="AY3" t="n">
-        <v>0.5055622458457947</v>
+        <v>0.05290534719824791</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2753594815731049</v>
+        <v>0.005099286325275898</v>
       </c>
       <c r="BA3" t="n">
-        <v>0.2698413729667664</v>
+        <v>0.1489344388246536</v>
       </c>
       <c r="BB3" t="n">
-        <v>0.286269873380661</v>
+        <v>0.01418015267699957</v>
       </c>
       <c r="BC3" t="n">
-        <v>0.3680351078510284</v>
+        <v>0.03283519297838211</v>
       </c>
       <c r="BD3" t="n">
-        <v>0.1718713790178299</v>
+        <v>0.1666922867298126</v>
       </c>
       <c r="BE3" t="n">
-        <v>0.6904993057250977</v>
+        <v>0.02235576137900352</v>
       </c>
       <c r="BF3" t="n">
-        <v>0.09491191804409027</v>
+        <v>0.0415765568614006</v>
       </c>
       <c r="BG3" t="n">
-        <v>0.469415009021759</v>
+        <v>0.08392542600631714</v>
       </c>
       <c r="BH3" t="n">
-        <v>0.4633021354675293</v>
+        <v>0.02147475630044937</v>
       </c>
       <c r="BI3" t="n">
-        <v>0.2646065354347229</v>
+        <v>0.04978268966078758</v>
       </c>
       <c r="BJ3" t="n">
-        <v>0.4127646684646606</v>
+        <v>0.04105242714285851</v>
       </c>
       <c r="BK3" t="n">
-        <v>0.2070077210664749</v>
+        <v>0.02171424031257629</v>
       </c>
       <c r="BL3" t="n">
-        <v>0.2129940688610077</v>
+        <v>0.05250927805900574</v>
       </c>
       <c r="BM3" t="n">
-        <v>0.1782512962818146</v>
+        <v>0.1400727182626724</v>
       </c>
       <c r="BN3" t="n">
-        <v>0.07985156029462814</v>
+        <v>0.04059536755084991</v>
       </c>
       <c r="BO3" t="n">
-        <v>0.1716185361146927</v>
+        <v>0.03510977327823639</v>
       </c>
       <c r="BP3" t="n">
-        <v>0.04647869989275932</v>
+        <v>0.0116798123344779</v>
       </c>
       <c r="BQ3" t="n">
-        <v>0.05750061571598053</v>
+        <v>0.02169300988316536</v>
       </c>
       <c r="BR3" t="n">
-        <v>0.1687432676553726</v>
+        <v>0.02300580404698849</v>
       </c>
       <c r="BS3" t="n">
-        <v>0.1284877061843872</v>
+        <v>0.04657203704118729</v>
       </c>
       <c r="BT3" t="n">
-        <v>0.1293830871582031</v>
+        <v>0.0382709801197052</v>
       </c>
       <c r="BU3" t="n">
-        <v>0.1079887896776199</v>
+        <v>0.02431120909750462</v>
       </c>
       <c r="BV3" t="n">
-        <v>0.5818776488304138</v>
+        <v>0.436507910490036</v>
       </c>
       <c r="BW3" t="n">
-        <v>0.04081545770168304</v>
+        <v>0.01862608268857002</v>
       </c>
       <c r="BX3" t="n">
-        <v>0.1698878705501556</v>
+        <v>0.001338716596364975</v>
       </c>
       <c r="BY3" t="n">
-        <v>0.1140867471694946</v>
+        <v>0.07409581542015076</v>
       </c>
       <c r="BZ3" t="n">
-        <v>0.03871618211269379</v>
+        <v>0.1468236148357391</v>
       </c>
       <c r="CA3" t="n">
-        <v>0.09352485090494156</v>
+        <v>0.01386217027902603</v>
       </c>
       <c r="CB3" t="n">
-        <v>0.08518358319997787</v>
+        <v>0.1185708343982697</v>
       </c>
       <c r="CC3" t="n">
-        <v>0.09473834931850433</v>
+        <v>0.000907018780708313</v>
       </c>
       <c r="CD3" t="n">
-        <v>0.2296673953533173</v>
+        <v>0.02895195782184601</v>
       </c>
       <c r="CE3" t="n">
-        <v>0.3629262447357178</v>
+        <v>0.2083925008773804</v>
       </c>
       <c r="CF3" t="n">
-        <v>0.02257594093680382</v>
+        <v>0.05230016261339188</v>
       </c>
       <c r="CG3" t="n">
-        <v>0.09614729881286621</v>
+        <v>0.04611730575561523</v>
       </c>
       <c r="CH3" t="n">
-        <v>0.1516747772693634</v>
+        <v>0.05162643641233444</v>
       </c>
       <c r="CI3" t="n">
-        <v>0.3004634976387024</v>
+        <v>0.04942786693572998</v>
       </c>
       <c r="CJ3" t="n">
-        <v>0.0301063247025013</v>
+        <v>0.01203525066375732</v>
       </c>
       <c r="CK3" t="n">
-        <v>0.06243042647838593</v>
+        <v>0.01197310816496611</v>
       </c>
       <c r="CL3" t="n">
-        <v>0.003684584051370621</v>
+        <v>0.02848088555037975</v>
       </c>
       <c r="CM3" t="n">
-        <v>0.4728636145591736</v>
+        <v>0.04608648642897606</v>
       </c>
       <c r="CN3" t="n">
-        <v>0.3200615346431732</v>
+        <v>0.2248261570930481</v>
       </c>
       <c r="CO3" t="n">
-        <v>0.3526913225650787</v>
+        <v>0.0243818461894989</v>
       </c>
       <c r="CP3" t="n">
-        <v>0.1962594836950302</v>
+        <v>0.1021692156791687</v>
       </c>
       <c r="CQ3" t="n">
-        <v>0.1648406088352203</v>
+        <v>0.045570969581604</v>
       </c>
       <c r="CR3" t="n">
-        <v>0.6001763939857483</v>
+        <v>0.06860492378473282</v>
       </c>
       <c r="CS3" t="n">
-        <v>0.1483259499073029</v>
+        <v>0.05121790617704391</v>
       </c>
       <c r="CT3" t="n">
-        <v>0.1058649867773056</v>
+        <v>0.01609573699533939</v>
       </c>
       <c r="CU3" t="n">
-        <v>0.2608199119567871</v>
+        <v>0.000609198585152626</v>
       </c>
       <c r="CV3" t="n">
-        <v>0.2627191543579102</v>
+        <v>0.01299099717289209</v>
       </c>
       <c r="CW3" t="n">
-        <v>0.362848311662674</v>
+        <v>0.2078087776899338</v>
       </c>
       <c r="CX3" t="n">
-        <v>0.0512436181306839</v>
+        <v>0.06446785479784012</v>
       </c>
       <c r="CY3" t="n">
-        <v>0.08537635207176208</v>
+        <v>0.04036080092191696</v>
       </c>
       <c r="CZ3" t="n">
-        <v>0.2103861570358276</v>
+        <v>0.05899657309055328</v>
       </c>
       <c r="DA3" t="n">
-        <v>0.2308364659547806</v>
+        <v>0.05589401349425316</v>
       </c>
       <c r="DB3" t="n">
-        <v>0.0189114473760128</v>
+        <v>0.02600426226854324</v>
       </c>
       <c r="DC3" t="n">
-        <v>0.1533087342977524</v>
+        <v>0.01682686060667038</v>
       </c>
       <c r="DD3" t="n">
-        <v>0.04962220042943954</v>
+        <v>0.01989557407796383</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.2154739499092102</v>
+        <v>0.1583883911371231</v>
       </c>
       <c r="DF3" t="n">
-        <v>0.9756681323051453</v>
+        <v>0.1215088367462158</v>
       </c>
       <c r="DG3" t="n">
-        <v>0.08787136524915695</v>
+        <v>0.0903184786438942</v>
       </c>
       <c r="DH3" t="n">
-        <v>0.1294090896844864</v>
+        <v>0.07572337239980698</v>
       </c>
       <c r="DI3" t="n">
-        <v>1.441456913948059</v>
+        <v>0.05334457755088806</v>
       </c>
       <c r="DJ3" t="n">
-        <v>0.1904006004333496</v>
+        <v>0.08076607435941696</v>
       </c>
       <c r="DK3" t="n">
-        <v>0.1807869076728821</v>
+        <v>0.01564722135663033</v>
       </c>
       <c r="DL3" t="n">
-        <v>0.4882193207740784</v>
+        <v>0.0197130274027586</v>
       </c>
       <c r="DM3" t="n">
-        <v>0.04447459429502487</v>
+        <v>0.06857314705848694</v>
       </c>
       <c r="DN3" t="n">
-        <v>0.1389538049697876</v>
+        <v>0.01207252126187086</v>
       </c>
       <c r="DO3" t="n">
-        <v>0.1914449334144592</v>
+        <v>0.1460499167442322</v>
       </c>
       <c r="DP3" t="n">
-        <v>0.05427855998277664</v>
+        <v>0.08104857802391052</v>
       </c>
       <c r="DQ3" t="n">
-        <v>0.1351292282342911</v>
+        <v>0.07383778691291809</v>
       </c>
       <c r="DR3" t="n">
-        <v>0.2695628702640533</v>
+        <v>0.06209760159254074</v>
       </c>
       <c r="DS3" t="n">
-        <v>0.1593413501977921</v>
+        <v>0.0917561873793602</v>
       </c>
       <c r="DT3" t="n">
-        <v>0.312691867351532</v>
+        <v>0.04585447534918785</v>
       </c>
       <c r="DU3" t="n">
-        <v>0.09541209042072296</v>
+        <v>0.02450099401175976</v>
       </c>
       <c r="DV3" t="n">
-        <v>0.02793424017727375</v>
+        <v>0.02905132248997688</v>
       </c>
       <c r="DW3" t="n">
-        <v>0.2710084915161133</v>
+        <v>0.05803830176591873</v>
       </c>
       <c r="DX3" t="n">
-        <v>0.1867446154356003</v>
+        <v>0.1667811423540115</v>
       </c>
       <c r="DY3" t="n">
-        <v>0.4590682685375214</v>
+        <v>0.02836512960493565</v>
       </c>
       <c r="DZ3" t="n">
-        <v>0.1494603306055069</v>
+        <v>0.02572307363152504</v>
       </c>
       <c r="EA3" t="n">
-        <v>0.157354936003685</v>
+        <v>0.05829990655183792</v>
       </c>
       <c r="EB3" t="n">
-        <v>0.1425206065177917</v>
+        <v>0.001498374855145812</v>
       </c>
       <c r="EC3" t="n">
-        <v>0.1029659658670425</v>
+        <v>0.1707553565502167</v>
       </c>
       <c r="ED3" t="n">
-        <v>0.2099073976278305</v>
+        <v>0.01024818979203701</v>
       </c>
       <c r="EE3" t="n">
-        <v>0.1517584174871445</v>
+        <v>0.005397394299507141</v>
       </c>
       <c r="EF3" t="n">
-        <v>0.4090233743190765</v>
+        <v>0.04734192788600922</v>
       </c>
       <c r="EG3" t="n">
-        <v>0.4466299712657928</v>
+        <v>0.1594085991382599</v>
       </c>
       <c r="EH3" t="n">
-        <v>0.2087397128343582</v>
+        <v>0.06169281899929047</v>
       </c>
       <c r="EI3" t="n">
-        <v>0.1059267967939377</v>
+        <v>0.05001974105834961</v>
       </c>
       <c r="EJ3" t="n">
-        <v>0.2392392009496689</v>
+        <v>0.07456927001476288</v>
       </c>
       <c r="EK3" t="n">
-        <v>0.4487168192863464</v>
+        <v>0.03305913135409355</v>
       </c>
       <c r="EL3" t="n">
-        <v>0.05259168148040771</v>
+        <v>0.02174339070916176</v>
       </c>
       <c r="EM3" t="n">
-        <v>0.1698781996965408</v>
+        <v>0.002222349168732762</v>
       </c>
       <c r="EN3" t="n">
-        <v>0.06016817688941956</v>
+        <v>0.04117777943611145</v>
       </c>
       <c r="EO3" t="n">
-        <v>0.2053266912698746</v>
+        <v>0.06376738101243973</v>
       </c>
       <c r="EP3" t="n">
-        <v>0.536840558052063</v>
+        <v>0.06879699230194092</v>
       </c>
       <c r="EQ3" t="n">
-        <v>0.1912144124507904</v>
+        <v>0.01607776060700417</v>
       </c>
       <c r="ER3" t="n">
-        <v>0.3625287115573883</v>
+        <v>0.06036772578954697</v>
       </c>
       <c r="ES3" t="n">
-        <v>0.09880931675434113</v>
+        <v>0.0195099301636219</v>
       </c>
       <c r="ET3" t="n">
-        <v>0.02085352689027786</v>
+        <v>0.05380505695939064</v>
       </c>
       <c r="EU3" t="n">
-        <v>0.06336862593889236</v>
+        <v>0.08238399028778076</v>
       </c>
       <c r="EV3" t="n">
-        <v>0.006462931632995605</v>
+        <v>0.09014365077018738</v>
       </c>
       <c r="EW3" t="n">
-        <v>0.1308233737945557</v>
+        <v>0.02740263007581234</v>
       </c>
       <c r="EX3" t="n">
-        <v>0.298697292804718</v>
+        <v>0.02831839397549629</v>
       </c>
       <c r="EY3" t="n">
-        <v>0.3965919613838196</v>
+        <v>0.1823855489492416</v>
       </c>
       <c r="EZ3" t="n">
-        <v>0.07768264412879944</v>
+        <v>0.06138321757316589</v>
       </c>
       <c r="FA3" t="n">
-        <v>0.1120639517903328</v>
+        <v>0.03394302725791931</v>
       </c>
       <c r="FB3" t="n">
-        <v>0.1112441122531891</v>
+        <v>0.03325260058045387</v>
       </c>
       <c r="FC3" t="n">
-        <v>0.2311831116676331</v>
+        <v>0.04566003382205963</v>
       </c>
       <c r="FD3" t="n">
-        <v>0.02923468314111233</v>
+        <v>0.002839533146470785</v>
       </c>
       <c r="FE3" t="n">
-        <v>0.1390579342842102</v>
+        <v>0.01310145389288664</v>
       </c>
       <c r="FF3" t="n">
-        <v>0.01815369352698326</v>
+        <v>0.0145459258928895</v>
       </c>
       <c r="FG3" t="n">
-        <v>0.2120906710624695</v>
+        <v>0.02263011410832405</v>
       </c>
       <c r="FH3" t="n">
-        <v>0.06639739125967026</v>
+        <v>0.01152637973427773</v>
       </c>
       <c r="FI3" t="n">
-        <v>0.4833585023880005</v>
+        <v>0.02235276065766811</v>
       </c>
       <c r="FJ3" t="n">
-        <v>0.1242836117744446</v>
+        <v>0.01391559839248657</v>
       </c>
       <c r="FK3" t="n">
-        <v>0.1784292608499527</v>
+        <v>0.0235001128166914</v>
       </c>
       <c r="FL3" t="n">
-        <v>0.183876171708107</v>
+        <v>0.04612276703119278</v>
       </c>
       <c r="FM3" t="n">
-        <v>0.2204391956329346</v>
+        <v>0.09193757921457291</v>
       </c>
       <c r="FN3" t="n">
-        <v>0.2727620005607605</v>
+        <v>0.09562256932258606</v>
       </c>
       <c r="FO3" t="n">
-        <v>0.1508009880781174</v>
+        <v>0.05490381643176079</v>
       </c>
       <c r="FP3" t="n">
-        <v>0.2836271524429321</v>
+        <v>0.23000368475914</v>
       </c>
       <c r="FQ3" t="n">
-        <v>0.2753211557865143</v>
+        <v>0.4946110248565674</v>
       </c>
       <c r="FR3" t="n">
-        <v>0.6069637537002563</v>
+        <v>0.09490228444337845</v>
       </c>
       <c r="FS3" t="n">
-        <v>0.2494206577539444</v>
+        <v>0.06011046096682549</v>
       </c>
       <c r="FT3" t="n">
-        <v>0.7157049179077148</v>
+        <v>0.1421141475439072</v>
       </c>
       <c r="FU3" t="n">
-        <v>0.1185944378376007</v>
+        <v>0.03758256137371063</v>
       </c>
       <c r="FV3" t="n">
-        <v>0.4964191913604736</v>
+        <v>0.04089832305908203</v>
       </c>
       <c r="FW3" t="n">
-        <v>0.02478277683258057</v>
+        <v>0.1943464875221252</v>
       </c>
       <c r="FX3" t="n">
-        <v>0.1290116310119629</v>
+        <v>0.08463054895401001</v>
       </c>
       <c r="FY3" t="n">
-        <v>0.3517719209194183</v>
+        <v>0.1839934438467026</v>
       </c>
       <c r="FZ3" t="n">
-        <v>0.03471817448735237</v>
+        <v>0.2275290489196777</v>
       </c>
       <c r="GA3" t="n">
-        <v>0.07291635870933533</v>
+        <v>0.1998273581266403</v>
       </c>
       <c r="GB3" t="n">
-        <v>0.04229593649506569</v>
+        <v>0.04604661837220192</v>
       </c>
       <c r="GC3" t="n">
-        <v>0.606695830821991</v>
+        <v>0.01935728639364243</v>
       </c>
       <c r="GD3" t="n">
-        <v>0.2911046743392944</v>
+        <v>0.06673707067966461</v>
       </c>
       <c r="GE3" t="n">
-        <v>0.1655148714780807</v>
+        <v>0.1282768100500107</v>
       </c>
       <c r="GF3" t="n">
-        <v>0.01053471490740776</v>
+        <v>0.0728871077299118</v>
       </c>
       <c r="GG3" t="n">
-        <v>0.1219512075185776</v>
+        <v>0.02439800836145878</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>0.001285805366933346</v>
+        <v>0.00126798078417778</v>
       </c>
       <c r="B4" t="n">
-        <v>0.1933411359786987</v>
+        <v>0.01599394902586937</v>
       </c>
       <c r="C4" t="n">
-        <v>0.01858674734830856</v>
+        <v>0.003160308813676238</v>
       </c>
       <c r="D4" t="n">
-        <v>0.02024329267442226</v>
+        <v>0.001570300897583365</v>
       </c>
       <c r="E4" t="n">
-        <v>0.01736352033913136</v>
+        <v>0.004263863433152437</v>
       </c>
       <c r="F4" t="n">
-        <v>0.1050152182579041</v>
+        <v>0.02634766139090061</v>
       </c>
       <c r="G4" t="n">
-        <v>0.006151802837848663</v>
+        <v>0.00353275379166007</v>
       </c>
       <c r="H4" t="n">
-        <v>0.0693708136677742</v>
+        <v>0.006376359611749649</v>
       </c>
       <c r="I4" t="n">
-        <v>0.04491038620471954</v>
+        <v>0.0006272949394769967</v>
       </c>
       <c r="J4" t="n">
-        <v>0.02953563258051872</v>
+        <v>0.003436088562011719</v>
       </c>
       <c r="K4" t="n">
-        <v>0.1553382724523544</v>
+        <v>0.02124801091849804</v>
       </c>
       <c r="L4" t="n">
-        <v>0.003288116538897157</v>
+        <v>0.004147323779761791</v>
       </c>
       <c r="M4" t="n">
-        <v>0.07209666818380356</v>
+        <v>0.00718882167711854</v>
       </c>
       <c r="N4" t="n">
-        <v>0.003216548822820187</v>
+        <v>0.007763897068798542</v>
       </c>
       <c r="O4" t="n">
-        <v>0.09119256585836411</v>
+        <v>0.03379342332482338</v>
       </c>
       <c r="P4" t="n">
-        <v>0.01707746088504791</v>
+        <v>0.003638815134763718</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.03031191974878311</v>
+        <v>0.004209368489682674</v>
       </c>
       <c r="R4" t="n">
-        <v>0.0663878321647644</v>
+        <v>9.337044321000576e-05</v>
       </c>
       <c r="S4" t="n">
-        <v>0.0002629586961120367</v>
+        <v>0.001674098311923444</v>
       </c>
       <c r="T4" t="n">
-        <v>0.01339320838451385</v>
+        <v>0.003194467164576054</v>
       </c>
       <c r="U4" t="n">
-        <v>0.00584298511967063</v>
+        <v>0.002262277761474252</v>
       </c>
       <c r="V4" t="n">
-        <v>0.001183819025754929</v>
+        <v>0.005528658162802458</v>
       </c>
       <c r="W4" t="n">
-        <v>0.02376552857458591</v>
+        <v>0.003514698939397931</v>
       </c>
       <c r="X4" t="n">
-        <v>6.811646744608879e-05</v>
+        <v>0.004352935589849949</v>
       </c>
       <c r="Y4" t="n">
-        <v>0.003808372188359499</v>
+        <v>0.0001886635436676443</v>
       </c>
       <c r="Z4" t="n">
-        <v>0.02589488215744495</v>
+        <v>0.004584372043609619</v>
       </c>
       <c r="AA4" t="n">
-        <v>0.002158377319574356</v>
+        <v>0.003922968171536922</v>
       </c>
       <c r="AB4" t="n">
-        <v>0.01104931812733412</v>
+        <v>0.00115834386087954</v>
       </c>
       <c r="AC4" t="n">
-        <v>0.02413652651011944</v>
+        <v>0.004233174026012421</v>
       </c>
       <c r="AD4" t="n">
-        <v>0.004476331640034914</v>
+        <v>0.0008502479176968336</v>
       </c>
       <c r="AE4" t="n">
-        <v>0.005419126246124506</v>
+        <v>0.00312015600502491</v>
       </c>
       <c r="AF4" t="n">
-        <v>0.02999370358884335</v>
+        <v>0.004443539772182703</v>
       </c>
       <c r="AG4" t="n">
-        <v>0.03173740208148956</v>
+        <v>0.006297086365520954</v>
       </c>
       <c r="AH4" t="n">
-        <v>0.003389675170183182</v>
+        <v>0.00159074948169291</v>
       </c>
       <c r="AI4" t="n">
-        <v>0.03502561151981354</v>
+        <v>0.01022271439433098</v>
       </c>
       <c r="AJ4" t="n">
-        <v>0.02680695056915283</v>
+        <v>0.001814846647903323</v>
       </c>
       <c r="AK4" t="n">
-        <v>0.006249148398637772</v>
+        <v>0.003520684782415628</v>
       </c>
       <c r="AL4" t="n">
-        <v>0.009233678691089153</v>
+        <v>0.004979144781827927</v>
       </c>
       <c r="AM4" t="n">
-        <v>0.001948462566360831</v>
+        <v>0.003498470177873969</v>
       </c>
       <c r="AN4" t="n">
-        <v>0.02557414211332798</v>
+        <v>0.002994289854541421</v>
       </c>
       <c r="AO4" t="n">
-        <v>0.0119406022131443</v>
+        <v>0.0004355837590992451</v>
       </c>
       <c r="AP4" t="n">
-        <v>0.03532391786575317</v>
+        <v>0.004192741122096777</v>
       </c>
       <c r="AQ4" t="n">
-        <v>0.02700909413397312</v>
+        <v>0.0004863592330366373</v>
       </c>
       <c r="AR4" t="n">
-        <v>0.01397517416626215</v>
+        <v>0.008237799629569054</v>
       </c>
       <c r="AS4" t="n">
-        <v>0.02284175343811512</v>
+        <v>0.001133086159825325</v>
       </c>
       <c r="AT4" t="n">
-        <v>0.02471575699746609</v>
+        <v>1.396983861923218e-05</v>
       </c>
       <c r="AU4" t="n">
-        <v>0.1059016659855843</v>
+        <v>0.02453762851655483</v>
       </c>
       <c r="AV4" t="n">
-        <v>0.008757907897233963</v>
+        <v>0.006429851055145264</v>
       </c>
       <c r="AW4" t="n">
-        <v>0.05616446956992149</v>
+        <v>0.002366807777434587</v>
       </c>
       <c r="AX4" t="n">
-        <v>0.0450446642935276</v>
+        <v>0.0085481908172369</v>
       </c>
       <c r="AY4" t="n">
-        <v>0.06481506675481796</v>
+        <v>0.02319748513400555</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.03224944695830345</v>
+        <v>0.0003751417680177838</v>
       </c>
       <c r="BA4" t="n">
-        <v>0.04909176379442215</v>
+        <v>0.004709661938250065</v>
       </c>
       <c r="BB4" t="n">
-        <v>0.02366337366402149</v>
+        <v>0.002152534434571862</v>
       </c>
       <c r="BC4" t="n">
-        <v>0.0001679891720414162</v>
+        <v>0.001431089825928211</v>
       </c>
       <c r="BD4" t="n">
-        <v>0.05099109560251236</v>
+        <v>0.007476986385881901</v>
       </c>
       <c r="BE4" t="n">
-        <v>0.03796237334609032</v>
+        <v>0.002925155218690634</v>
       </c>
       <c r="BF4" t="n">
-        <v>0.02436706051230431</v>
+        <v>0.0004702174046542495</v>
       </c>
       <c r="BG4" t="n">
-        <v>0.04417165368795395</v>
+        <v>0.001083557261154056</v>
       </c>
       <c r="BH4" t="n">
-        <v>0.05290310829877853</v>
+        <v>0.0001325516495853662</v>
       </c>
       <c r="BI4" t="n">
-        <v>0.03190958499908447</v>
+        <v>0.0004530629958026111</v>
       </c>
       <c r="BJ4" t="n">
-        <v>0.01675882935523987</v>
+        <v>0.001580805750563741</v>
       </c>
       <c r="BK4" t="n">
-        <v>0.04203644394874573</v>
+        <v>0.002900814171880484</v>
       </c>
       <c r="BL4" t="n">
-        <v>0.008175617083907127</v>
+        <v>0.003477462567389011</v>
       </c>
       <c r="BM4" t="n">
-        <v>0.02676533535122871</v>
+        <v>0.00515602994710207</v>
       </c>
       <c r="BN4" t="n">
-        <v>0.014508874155581</v>
+        <v>0.0022521095816046</v>
       </c>
       <c r="BO4" t="n">
-        <v>0.002592766657471657</v>
+        <v>0.002506046323105693</v>
       </c>
       <c r="BP4" t="n">
-        <v>0.01205857750028372</v>
+        <v>0.004539923276752234</v>
       </c>
       <c r="BQ4" t="n">
-        <v>0.005181241780519485</v>
+        <v>0.002789030550047755</v>
       </c>
       <c r="BR4" t="n">
-        <v>0.0216765720397234</v>
+        <v>0.002057510428130627</v>
       </c>
       <c r="BS4" t="n">
-        <v>0.03070604242384434</v>
+        <v>0.0005482678534463048</v>
       </c>
       <c r="BT4" t="n">
-        <v>0.01492025144398212</v>
+        <v>0.003590912790969014</v>
       </c>
       <c r="BU4" t="n">
-        <v>0.005982058122754097</v>
+        <v>0.0004197652451694012</v>
       </c>
       <c r="BV4" t="n">
-        <v>0.05421336740255356</v>
+        <v>0.0128452442586422</v>
       </c>
       <c r="BW4" t="n">
-        <v>0.02562107145786285</v>
+        <v>0.001896411180496216</v>
       </c>
       <c r="BX4" t="n">
-        <v>0.03000326454639435</v>
+        <v>0.001798106008209288</v>
       </c>
       <c r="BY4" t="n">
-        <v>0.01464228145778179</v>
+        <v>0.002045899629592896</v>
       </c>
       <c r="BZ4" t="n">
-        <v>0.02090359851717949</v>
+        <v>0.01238006073981524</v>
       </c>
       <c r="CA4" t="n">
-        <v>0.009184342809021473</v>
+        <v>0.004006762523204088</v>
       </c>
       <c r="CB4" t="n">
-        <v>0.02662133798003197</v>
+        <v>0.004664219915866852</v>
       </c>
       <c r="CC4" t="n">
-        <v>0.008354527875781059</v>
+        <v>0.001441531581804156</v>
       </c>
       <c r="CD4" t="n">
-        <v>0.00158564408775419</v>
+        <v>0.003834708826616406</v>
       </c>
       <c r="CE4" t="n">
-        <v>0.0368083082139492</v>
+        <v>0.006599230226129293</v>
       </c>
       <c r="CF4" t="n">
-        <v>0.008901618421077728</v>
+        <v>0.000731868261937052</v>
       </c>
       <c r="CG4" t="n">
-        <v>0.004253643099218607</v>
+        <v>0.0007547058630734682</v>
       </c>
       <c r="CH4" t="n">
-        <v>0.01473313104361296</v>
+        <v>0.000458172638900578</v>
       </c>
       <c r="CI4" t="n">
-        <v>0.005113591440021992</v>
+        <v>0.007267438340932131</v>
       </c>
       <c r="CJ4" t="n">
-        <v>0.01289563253521919</v>
+        <v>0.001693750265985727</v>
       </c>
       <c r="CK4" t="n">
-        <v>0.0001887744292616844</v>
+        <v>0.001262479927390814</v>
       </c>
       <c r="CL4" t="n">
-        <v>0.007285506930202246</v>
+        <v>0.00119605811778456</v>
       </c>
       <c r="CM4" t="n">
-        <v>0.02801518887281418</v>
+        <v>0.006081592291593552</v>
       </c>
       <c r="CN4" t="n">
-        <v>0.02183796092867851</v>
+        <v>0.006576234009116888</v>
       </c>
       <c r="CO4" t="n">
-        <v>0.000506955198943615</v>
+        <v>0.006608004681766033</v>
       </c>
       <c r="CP4" t="n">
-        <v>0.07696776837110519</v>
+        <v>0.004191989544779062</v>
       </c>
       <c r="CQ4" t="n">
-        <v>0.003709404729306698</v>
+        <v>0.00700641144067049</v>
       </c>
       <c r="CR4" t="n">
-        <v>0.01551679987460375</v>
+        <v>0.00488888006657362</v>
       </c>
       <c r="CS4" t="n">
-        <v>0.03439835831522942</v>
+        <v>0.0006124549545347691</v>
       </c>
       <c r="CT4" t="n">
-        <v>0.01976515911519527</v>
+        <v>0.005122446920722723</v>
       </c>
       <c r="CU4" t="n">
-        <v>0.01073584333062172</v>
+        <v>0.003031858010217547</v>
       </c>
       <c r="CV4" t="n">
-        <v>0.00227186200208962</v>
+        <v>0.004915416240692139</v>
       </c>
       <c r="CW4" t="n">
-        <v>0.03021443448960781</v>
+        <v>0.005930564366281033</v>
       </c>
       <c r="CX4" t="n">
-        <v>0.01433246675878763</v>
+        <v>0.001190533163025975</v>
       </c>
       <c r="CY4" t="n">
-        <v>0.006710660178214312</v>
+        <v>0.001781396917067468</v>
       </c>
       <c r="CZ4" t="n">
-        <v>0.02010669372975826</v>
+        <v>0.0005189800867810845</v>
       </c>
       <c r="DA4" t="n">
-        <v>0.00594901479780674</v>
+        <v>0.007566506508737803</v>
       </c>
       <c r="DB4" t="n">
-        <v>0.01028226222842932</v>
+        <v>0.0007144112605601549</v>
       </c>
       <c r="DC4" t="n">
-        <v>0.008160820230841637</v>
+        <v>0.0009250151924788952</v>
       </c>
       <c r="DD4" t="n">
-        <v>0.01278581283986568</v>
+        <v>0.0003774788056034595</v>
       </c>
       <c r="DE4" t="n">
-        <v>0.00287052383646369</v>
+        <v>0.005618765018880367</v>
       </c>
       <c r="DF4" t="n">
-        <v>0.03707844018936157</v>
+        <v>0.002059075050055981</v>
       </c>
       <c r="DG4" t="n">
-        <v>0.004572446458041668</v>
+        <v>0.004866203293204308</v>
       </c>
       <c r="DH4" t="n">
-        <v>0.02449434064328671</v>
+        <v>0.0001979291555471718</v>
       </c>
       <c r="DI4" t="n">
-        <v>0.03947596997022629</v>
+        <v>0.002471458166837692</v>
       </c>
       <c r="DJ4" t="n">
-        <v>0.07792548090219498</v>
+        <v>0.007358681876212358</v>
       </c>
       <c r="DK4" t="n">
-        <v>0.03896672278642654</v>
+        <v>0.004442948848009109</v>
       </c>
       <c r="DL4" t="n">
-        <v>0.01902885362505913</v>
+        <v>0.005161814391613007</v>
       </c>
       <c r="DM4" t="n">
-        <v>0.04573852568864822</v>
+        <v>0.002580844797194004</v>
       </c>
       <c r="DN4" t="n">
-        <v>0.001716473256237805</v>
+        <v>0.003241853090003133</v>
       </c>
       <c r="DO4" t="n">
-        <v>0.02193335257470608</v>
+        <v>0.004402432590723038</v>
       </c>
       <c r="DP4" t="n">
-        <v>0.01232796534895897</v>
+        <v>0.00011039013043046</v>
       </c>
       <c r="DQ4" t="n">
-        <v>0.01336309313774109</v>
+        <v>0.004040793050080538</v>
       </c>
       <c r="DR4" t="n">
-        <v>0.0001268740743398666</v>
+        <v>0.0009549793903715909</v>
       </c>
       <c r="DS4" t="n">
-        <v>0.02263557352125645</v>
+        <v>0.004088611342012882</v>
       </c>
       <c r="DT4" t="n">
-        <v>0.03313284367322922</v>
+        <v>0.002410057932138443</v>
       </c>
       <c r="DU4" t="n">
-        <v>0.01278025005012751</v>
+        <v>0.002784052165225148</v>
       </c>
       <c r="DV4" t="n">
-        <v>0.003874193178489804</v>
+        <v>0.00166675983928144</v>
       </c>
       <c r="DW4" t="n">
-        <v>0.003944097086787224</v>
+        <v>0.0006239563226699829</v>
       </c>
       <c r="DX4" t="n">
-        <v>0.01653840951621532</v>
+        <v>0.001282952958717942</v>
       </c>
       <c r="DY4" t="n">
-        <v>0.01244417950510979</v>
+        <v>0.007477355189621449</v>
       </c>
       <c r="DZ4" t="n">
-        <v>0.03654568269848824</v>
+        <v>0.0002143626334145665</v>
       </c>
       <c r="EA4" t="n">
-        <v>0.005615177564322948</v>
+        <v>0.0002690856344997883</v>
       </c>
       <c r="EB4" t="n">
-        <v>0.007376863155514002</v>
+        <v>0.004723664373159409</v>
       </c>
       <c r="EC4" t="n">
-        <v>0.003000342752784491</v>
+        <v>0.003218692494556308</v>
       </c>
       <c r="ED4" t="n">
-        <v>0.01841890253126621</v>
+        <v>0.004108014516532421</v>
       </c>
       <c r="EE4" t="n">
-        <v>0.03940056636929512</v>
+        <v>0.004349291790276766</v>
       </c>
       <c r="EF4" t="n">
-        <v>0.003085985314100981</v>
+        <v>0.003282275283709168</v>
       </c>
       <c r="EG4" t="n">
-        <v>0.02818982303142548</v>
+        <v>0.001879154704511166</v>
       </c>
       <c r="EH4" t="n">
-        <v>0.003746179398149252</v>
+        <v>0.001127672614529729</v>
       </c>
       <c r="EI4" t="n">
-        <v>0.0195523276925087</v>
+        <v>0.000211819977266714</v>
       </c>
       <c r="EJ4" t="n">
-        <v>0.01143449544906616</v>
+        <v>0.001922356663271785</v>
       </c>
       <c r="EK4" t="n">
-        <v>0.0348355807363987</v>
+        <v>0.003935615997761488</v>
       </c>
       <c r="EL4" t="n">
-        <v>0.02999402582645416</v>
+        <v>0.0003264343831688166</v>
       </c>
       <c r="EM4" t="n">
-        <v>0.006102345418184996</v>
+        <v>0.003125962801277637</v>
       </c>
       <c r="EN4" t="n">
-        <v>0.003910715226083994</v>
+        <v>0.001565017271786928</v>
       </c>
       <c r="EO4" t="n">
-        <v>0.005212598480284214</v>
+        <v>0.002690891269594431</v>
       </c>
       <c r="EP4" t="n">
-        <v>0.01966446451842785</v>
+        <v>0.005845819599926472</v>
       </c>
       <c r="EQ4" t="n">
-        <v>0.01387121342122555</v>
+        <v>0.0008272599661722779</v>
       </c>
       <c r="ER4" t="n">
-        <v>0.01585554331541061</v>
+        <v>0.002879590494558215</v>
       </c>
       <c r="ES4" t="n">
-        <v>0.009723211638629436</v>
+        <v>0.001009892788715661</v>
       </c>
       <c r="ET4" t="n">
-        <v>0.0008639395236968994</v>
+        <v>0.001089169410988688</v>
       </c>
       <c r="EU4" t="n">
-        <v>0.04067007079720497</v>
+        <v>0.002277641091495752</v>
       </c>
       <c r="EV4" t="n">
-        <v>0.01028389949351549</v>
+        <v>0.001739806728437543</v>
       </c>
       <c r="EW4" t="n">
-        <v>0.00326214637607336</v>
+        <v>0.001503748004324734</v>
       </c>
       <c r="EX4" t="n">
-        <v>0.003556367009878159</v>
+        <v>0.004262535832822323</v>
       </c>
       <c r="EY4" t="n">
-        <v>0.03200646117329597</v>
+        <v>0.006937364116311073</v>
       </c>
       <c r="EZ4" t="n">
-        <v>0.006347133778035641</v>
+        <v>0.001204413827508688</v>
       </c>
       <c r="FA4" t="n">
-        <v>0.004040193744003773</v>
+        <v>0.00114932400174439</v>
       </c>
       <c r="FB4" t="n">
-        <v>0.02269059047102928</v>
+        <v>0.0007048803381621838</v>
       </c>
       <c r="FC4" t="n">
-        <v>0.00802516657859087</v>
+        <v>0.007217356003820896</v>
       </c>
       <c r="FD4" t="n">
-        <v>0.02168634906411171</v>
+        <v>0.001781421946361661</v>
       </c>
       <c r="FE4" t="n">
-        <v>0.005019897129386663</v>
+        <v>0.001014235545881093</v>
       </c>
       <c r="FF4" t="n">
-        <v>0.01941293105483055</v>
+        <v>0.0006092184339649975</v>
       </c>
       <c r="FG4" t="n">
-        <v>0.007748027797788382</v>
+        <v>0.002403879072517157</v>
       </c>
       <c r="FH4" t="n">
-        <v>0.001693285536020994</v>
+        <v>0.004194100853055716</v>
       </c>
       <c r="FI4" t="n">
-        <v>0.008176573552191257</v>
+        <v>0.005424591712653637</v>
       </c>
       <c r="FJ4" t="n">
-        <v>0.03212658315896988</v>
+        <v>0.003935681190341711</v>
       </c>
       <c r="FK4" t="n">
-        <v>0.02829266712069511</v>
+        <v>0.001626058015972376</v>
       </c>
       <c r="FL4" t="n">
-        <v>0.01334808301180601</v>
+        <v>0.008104941807687283</v>
       </c>
       <c r="FM4" t="n">
-        <v>0.004959762096405029</v>
+        <v>0.0007546475389972329</v>
       </c>
       <c r="FN4" t="n">
-        <v>0.01897978968918324</v>
+        <v>0.008763554506003857</v>
       </c>
       <c r="FO4" t="n">
-        <v>0.01188160572201014</v>
+        <v>0.00713932141661644</v>
       </c>
       <c r="FP4" t="n">
-        <v>0.02168457396328449</v>
+        <v>0.003116722917184234</v>
       </c>
       <c r="FQ4" t="n">
-        <v>0.02256599441170692</v>
+        <v>0.003402253147214651</v>
       </c>
       <c r="FR4" t="n">
-        <v>0.008071425370872021</v>
+        <v>0.00517134927213192</v>
       </c>
       <c r="FS4" t="n">
-        <v>0.0008374499157071114</v>
+        <v>0.0002227588556706905</v>
       </c>
       <c r="FT4" t="n">
-        <v>0.0009262491948902607</v>
+        <v>0.003684319322928786</v>
       </c>
       <c r="FU4" t="n">
-        <v>0.04882736131548882</v>
+        <v>0.003262128680944443</v>
       </c>
       <c r="FV4" t="n">
-        <v>0.01786950044333935</v>
+        <v>0.001686154864728451</v>
       </c>
       <c r="FW4" t="n">
-        <v>0.01899264752864838</v>
+        <v>0.009782219305634499</v>
       </c>
       <c r="FX4" t="n">
-        <v>0.008742416277527809</v>
+        <v>0.0001356648863293231</v>
       </c>
       <c r="FY4" t="n">
-        <v>0.03087994828820229</v>
+        <v>2.541147296142299e-05</v>
       </c>
       <c r="FZ4" t="n">
-        <v>0.009556470438838005</v>
+        <v>0.002608340233564377</v>
       </c>
       <c r="GA4" t="n">
-        <v>0.008657507598400116</v>
+        <v>0.007388897240161896</v>
       </c>
       <c r="GB4" t="n">
-        <v>0.0041235676035285</v>
+        <v>0.001856315182521939</v>
       </c>
       <c r="GC4" t="n">
-        <v>0.005143224261701107</v>
+        <v>0.01135748066008091</v>
       </c>
       <c r="GD4" t="n">
-        <v>0.03165294975042343</v>
+        <v>0.003765454981476068</v>
       </c>
       <c r="GE4" t="n">
-        <v>0.02424420043826103</v>
+        <v>0.000678237178362906</v>
       </c>
       <c r="GF4" t="n">
-        <v>0.01382377650588751</v>
+        <v>0.0004407633095979691</v>
       </c>
       <c r="GG4" t="n">
-        <v>0.007610555738210678</v>
+        <v>0.003687075804919004</v>
       </c>
     </row>
     <row r="5">
@@ -3275,1140 +3275,1140 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>0.0005928369937464595</v>
+        <v>0.0001092152670025826</v>
       </c>
       <c r="B6" t="n">
-        <v>0.002426889492198825</v>
+        <v>0.1197506934404373</v>
       </c>
       <c r="C6" t="n">
-        <v>0.0004222870920784771</v>
+        <v>0.008882930502295494</v>
       </c>
       <c r="D6" t="n">
-        <v>0.000706691644154489</v>
+        <v>0.02388284355401993</v>
       </c>
       <c r="E6" t="n">
-        <v>0.001911196857690811</v>
+        <v>0.006862024776637554</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0005675768479704857</v>
+        <v>0.02916711196303368</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0002005794522119686</v>
+        <v>0.03572604060173035</v>
       </c>
       <c r="H6" t="n">
-        <v>3.863043457386084e-05</v>
+        <v>0.03781819716095924</v>
       </c>
       <c r="I6" t="n">
-        <v>0.0001641650596866384</v>
+        <v>0.01635561510920525</v>
       </c>
       <c r="J6" t="n">
-        <v>0.000126018567243591</v>
+        <v>0.02730333060026169</v>
       </c>
       <c r="K6" t="n">
-        <v>0.001436837832443416</v>
+        <v>0.1204361468553543</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0002662838087417185</v>
+        <v>0.009492063894867897</v>
       </c>
       <c r="M6" t="n">
-        <v>0.0008169747306965292</v>
+        <v>0.06237486004829407</v>
       </c>
       <c r="N6" t="n">
-        <v>0.001993207959458232</v>
+        <v>0.05277666077017784</v>
       </c>
       <c r="O6" t="n">
-        <v>0.0007512776646763086</v>
+        <v>0.02656513080000877</v>
       </c>
       <c r="P6" t="n">
-        <v>0.0001725453766994178</v>
+        <v>0.009433434344828129</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.0003128133248537779</v>
+        <v>0.02946503646671772</v>
       </c>
       <c r="R6" t="n">
-        <v>5.469885945785791e-05</v>
+        <v>0.0499129593372345</v>
       </c>
       <c r="S6" t="n">
-        <v>4.531181184574962e-05</v>
+        <v>0.01254626084119081</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0006311146426014602</v>
+        <v>0.05145162343978882</v>
       </c>
       <c r="U6" t="n">
-        <v>1.555506514705485e-07</v>
+        <v>0.005772322416305542</v>
       </c>
       <c r="V6" t="n">
-        <v>0.0002270076947752386</v>
+        <v>0.02436027862131596</v>
       </c>
       <c r="W6" t="n">
-        <v>8.921424159780145e-05</v>
+        <v>0.01049115229398012</v>
       </c>
       <c r="X6" t="n">
-        <v>0.0004048015689477324</v>
+        <v>0.01984349638223648</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.0002012817858485505</v>
+        <v>0.002383447950705886</v>
       </c>
       <c r="Z6" t="n">
-        <v>9.54220668063499e-05</v>
+        <v>0.013673753477633</v>
       </c>
       <c r="AA6" t="n">
-        <v>9.39203891903162e-05</v>
+        <v>0.004135806113481522</v>
       </c>
       <c r="AB6" t="n">
-        <v>2.824708644766361e-05</v>
+        <v>0.008507322520017624</v>
       </c>
       <c r="AC6" t="n">
-        <v>0.000528322474565357</v>
+        <v>0.0008552016224712133</v>
       </c>
       <c r="AD6" t="n">
-        <v>0.0003425660252105445</v>
+        <v>0.0052185975946486</v>
       </c>
       <c r="AE6" t="n">
-        <v>0.0003717084182426333</v>
+        <v>0.02460101991891861</v>
       </c>
       <c r="AF6" t="n">
-        <v>8.2053491496481e-05</v>
+        <v>0.03341452404856682</v>
       </c>
       <c r="AG6" t="n">
-        <v>4.321358210290782e-05</v>
+        <v>0.02303392998874187</v>
       </c>
       <c r="AH6" t="n">
-        <v>0.0005324189551174641</v>
+        <v>0.0009339991956949234</v>
       </c>
       <c r="AI6" t="n">
-        <v>0.0001437977334717289</v>
+        <v>0.04668024182319641</v>
       </c>
       <c r="AJ6" t="n">
-        <v>0.0001024220400722697</v>
+        <v>0.007582924328744411</v>
       </c>
       <c r="AK6" t="n">
-        <v>0.0003569434629753232</v>
+        <v>0.011304278858006</v>
       </c>
       <c r="AL6" t="n">
-        <v>0.0005952176288701594</v>
+        <v>0.03102584928274155</v>
       </c>
       <c r="AM6" t="n">
-        <v>0.0001751185045577586</v>
+        <v>0.006694570183753967</v>
       </c>
       <c r="AN6" t="n">
-        <v>8.255569991888478e-05</v>
+        <v>0.02252328768372536</v>
       </c>
       <c r="AO6" t="n">
-        <v>0.0002353657182538882</v>
+        <v>0.008998474106192589</v>
       </c>
       <c r="AP6" t="n">
-        <v>0.0003457814455032349</v>
+        <v>0.0109582431614399</v>
       </c>
       <c r="AQ6" t="n">
-        <v>0.0001362803159281611</v>
+        <v>0.000200582027900964</v>
       </c>
       <c r="AR6" t="n">
-        <v>0.0001019876726786606</v>
+        <v>0.05333464220166206</v>
       </c>
       <c r="AS6" t="n">
-        <v>8.851222810335457e-05</v>
+        <v>0.01194997783750296</v>
       </c>
       <c r="AT6" t="n">
-        <v>0.0003413396771065891</v>
+        <v>0.001693574711680412</v>
       </c>
       <c r="AU6" t="n">
-        <v>0.002249531447887421</v>
+        <v>0.1257407516241074</v>
       </c>
       <c r="AV6" t="n">
-        <v>8.625615737400949e-05</v>
+        <v>0.002167092636227608</v>
       </c>
       <c r="AW6" t="n">
-        <v>5.971541395410895e-05</v>
+        <v>0.008302563801407814</v>
       </c>
       <c r="AX6" t="n">
-        <v>0.0001724819303490222</v>
+        <v>0.01677347347140312</v>
       </c>
       <c r="AY6" t="n">
-        <v>0.0004557110369205475</v>
+        <v>0.03424093872308731</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.0001580195676069707</v>
+        <v>0.007064294070005417</v>
       </c>
       <c r="BA6" t="n">
-        <v>0.0001527471613371745</v>
+        <v>0.0195038877427578</v>
       </c>
       <c r="BB6" t="n">
-        <v>0.0001495105243520811</v>
+        <v>0.008795928210020065</v>
       </c>
       <c r="BC6" t="n">
-        <v>0.0001328131183981895</v>
+        <v>0.004559063352644444</v>
       </c>
       <c r="BD6" t="n">
-        <v>0.0002415414055576548</v>
+        <v>0.02102216705679893</v>
       </c>
       <c r="BE6" t="n">
-        <v>4.551317397272214e-05</v>
+        <v>0.01920752972364426</v>
       </c>
       <c r="BF6" t="n">
-        <v>0.0003054765402339399</v>
+        <v>0.02198161371052265</v>
       </c>
       <c r="BG6" t="n">
-        <v>0.001281976932659745</v>
+        <v>0.04421704262495041</v>
       </c>
       <c r="BH6" t="n">
-        <v>0.0001662624854361638</v>
+        <v>0.004463046789169312</v>
       </c>
       <c r="BI6" t="n">
-        <v>0.0002902179548982531</v>
+        <v>0.02228951826691628</v>
       </c>
       <c r="BJ6" t="n">
-        <v>0.0003277729556430131</v>
+        <v>0.005810388829559088</v>
       </c>
       <c r="BK6" t="n">
-        <v>0.0001823071215767413</v>
+        <v>0.01115477457642555</v>
       </c>
       <c r="BL6" t="n">
-        <v>0.0003754000645130873</v>
+        <v>0.000135310459882021</v>
       </c>
       <c r="BM6" t="n">
-        <v>0.00058470678050071</v>
+        <v>0.00789747666567564</v>
       </c>
       <c r="BN6" t="n">
-        <v>5.799433893116657e-07</v>
+        <v>0.01577932760119438</v>
       </c>
       <c r="BO6" t="n">
-        <v>0.0004960802034474909</v>
+        <v>0.01963412016630173</v>
       </c>
       <c r="BP6" t="n">
-        <v>0.000627711764536798</v>
+        <v>0.01787529699504375</v>
       </c>
       <c r="BQ6" t="n">
-        <v>0.0001830641849664971</v>
+        <v>0.01173835527151823</v>
       </c>
       <c r="BR6" t="n">
-        <v>0.0002092650975100696</v>
+        <v>0.02073502540588379</v>
       </c>
       <c r="BS6" t="n">
-        <v>4.510275539360009e-05</v>
+        <v>0.005286508239805698</v>
       </c>
       <c r="BT6" t="n">
-        <v>3.031392407137901e-05</v>
+        <v>0.01156623288989067</v>
       </c>
       <c r="BU6" t="n">
-        <v>0.0001700671418802813</v>
+        <v>0.02312184683978558</v>
       </c>
       <c r="BV6" t="n">
-        <v>0.001091136829927564</v>
+        <v>0.1170605793595314</v>
       </c>
       <c r="BW6" t="n">
-        <v>0.0003835895622614771</v>
+        <v>0.0170537605881691</v>
       </c>
       <c r="BX6" t="n">
-        <v>2.67311988864094e-05</v>
+        <v>0.03269737586379051</v>
       </c>
       <c r="BY6" t="n">
-        <v>0.0005157852428965271</v>
+        <v>0.01979010924696922</v>
       </c>
       <c r="BZ6" t="n">
-        <v>0.0006685405387543142</v>
+        <v>0.005297727882862091</v>
       </c>
       <c r="CA6" t="n">
-        <v>0.0001081461232388392</v>
+        <v>0.02076973766088486</v>
       </c>
       <c r="CB6" t="n">
-        <v>0.0001315137778874487</v>
+        <v>0.00905684195458889</v>
       </c>
       <c r="CC6" t="n">
-        <v>5.777343176305294e-05</v>
+        <v>0.002168952487409115</v>
       </c>
       <c r="CD6" t="n">
-        <v>7.377384463325143e-05</v>
+        <v>0.01022745296359062</v>
       </c>
       <c r="CE6" t="n">
-        <v>0.0004576830542646348</v>
+        <v>0.03939617425203323</v>
       </c>
       <c r="CF6" t="n">
-        <v>3.571091656340286e-05</v>
+        <v>0.004733562469482422</v>
       </c>
       <c r="CG6" t="n">
-        <v>0.0002371254522586241</v>
+        <v>0.001939244568347931</v>
       </c>
       <c r="CH6" t="n">
-        <v>0.0002118188131134957</v>
+        <v>0.003243034705519676</v>
       </c>
       <c r="CI6" t="n">
-        <v>0.0002067947934847325</v>
+        <v>0.006049733608961105</v>
       </c>
       <c r="CJ6" t="n">
-        <v>0.0001155209756689146</v>
+        <v>0.002603606088086963</v>
       </c>
       <c r="CK6" t="n">
-        <v>1.605634133738931e-05</v>
+        <v>0.0004965115804225206</v>
       </c>
       <c r="CL6" t="n">
-        <v>6.85317900206428e-06</v>
+        <v>0.003280914621427655</v>
       </c>
       <c r="CM6" t="n">
-        <v>0.0004627335583791137</v>
+        <v>0.01680555567145348</v>
       </c>
       <c r="CN6" t="n">
-        <v>0.0002982202277053148</v>
+        <v>0.06751815974712372</v>
       </c>
       <c r="CO6" t="n">
-        <v>0.0002999030402861536</v>
+        <v>0.002423182362690568</v>
       </c>
       <c r="CP6" t="n">
-        <v>1.020453055389225e-05</v>
+        <v>0.03804277628660202</v>
       </c>
       <c r="CQ6" t="n">
-        <v>0.0003690349985845387</v>
+        <v>0.02797552011907101</v>
       </c>
       <c r="CR6" t="n">
-        <v>0.0002239793102489784</v>
+        <v>0.01074084360152483</v>
       </c>
       <c r="CS6" t="n">
-        <v>1.503155181126203e-05</v>
+        <v>0.01079856790602207</v>
       </c>
       <c r="CT6" t="n">
-        <v>0.000191947357961908</v>
+        <v>0.02075517177581787</v>
       </c>
       <c r="CU6" t="n">
-        <v>2.114972085109912e-05</v>
+        <v>0.003609186504036188</v>
       </c>
       <c r="CV6" t="n">
-        <v>7.831552647985518e-05</v>
+        <v>0.00273875892162323</v>
       </c>
       <c r="CW6" t="n">
-        <v>0.0002710366970859468</v>
+        <v>0.03710872679948807</v>
       </c>
       <c r="CX6" t="n">
-        <v>1.402823818352772e-05</v>
+        <v>0.005727310664951801</v>
       </c>
       <c r="CY6" t="n">
-        <v>0.0003357913519721478</v>
+        <v>0.004837153479456902</v>
       </c>
       <c r="CZ6" t="n">
-        <v>0.0001853438443504274</v>
+        <v>0.004184203688055277</v>
       </c>
       <c r="DA6" t="n">
-        <v>0.0002977624535560608</v>
+        <v>0.007396834902465343</v>
       </c>
       <c r="DB6" t="n">
-        <v>0.0001052957159117796</v>
+        <v>0.00269135576672852</v>
       </c>
       <c r="DC6" t="n">
-        <v>2.780305294436403e-06</v>
+        <v>0.001176149351522326</v>
       </c>
       <c r="DD6" t="n">
-        <v>6.144073267932981e-05</v>
+        <v>0.002585786394774914</v>
       </c>
       <c r="DE6" t="n">
-        <v>0.0001125173876062036</v>
+        <v>0.003638297319412231</v>
       </c>
       <c r="DF6" t="n">
-        <v>0.0007207500166259706</v>
+        <v>0.07262679934501648</v>
       </c>
       <c r="DG6" t="n">
-        <v>6.885649781906977e-05</v>
+        <v>0.03471501171588898</v>
       </c>
       <c r="DH6" t="n">
-        <v>0.0003897499991580844</v>
+        <v>0.004706596024334431</v>
       </c>
       <c r="DI6" t="n">
-        <v>0.0006943329353816807</v>
+        <v>0.02871675416827202</v>
       </c>
       <c r="DJ6" t="n">
-        <v>0.0001741745218168944</v>
+        <v>0.05177845805883408</v>
       </c>
       <c r="DK6" t="n">
-        <v>0.0006663427921012044</v>
+        <v>0.008352109231054783</v>
       </c>
       <c r="DL6" t="n">
-        <v>5.82558277528733e-05</v>
+        <v>0.0351320281624794</v>
       </c>
       <c r="DM6" t="n">
-        <v>0.0003367211320437491</v>
+        <v>0.02632488682866096</v>
       </c>
       <c r="DN6" t="n">
-        <v>0.0004982901155017316</v>
+        <v>6.879772990942001e-05</v>
       </c>
       <c r="DO6" t="n">
-        <v>0.0002873917983379215</v>
+        <v>0.023256441578269</v>
       </c>
       <c r="DP6" t="n">
-        <v>3.235672920709476e-07</v>
+        <v>0.006515787914395332</v>
       </c>
       <c r="DQ6" t="n">
-        <v>0.0004097339406143874</v>
+        <v>0.02024956420063972</v>
       </c>
       <c r="DR6" t="n">
-        <v>4.247968172421679e-05</v>
+        <v>0.009138628840446472</v>
       </c>
       <c r="DS6" t="n">
-        <v>6.377600220730528e-05</v>
+        <v>0.01523718237876892</v>
       </c>
       <c r="DT6" t="n">
-        <v>3.228071000194177e-05</v>
+        <v>0.01858966052532196</v>
       </c>
       <c r="DU6" t="n">
-        <v>0.0002742154756560922</v>
+        <v>0.01703156344592571</v>
       </c>
       <c r="DV6" t="n">
-        <v>5.004416379961185e-06</v>
+        <v>0.002857366343960166</v>
       </c>
       <c r="DW6" t="n">
-        <v>2.670452522579581e-05</v>
+        <v>0.01252347603440285</v>
       </c>
       <c r="DX6" t="n">
-        <v>0.0002479137328919023</v>
+        <v>0.01482905726879835</v>
       </c>
       <c r="DY6" t="n">
-        <v>0.0003915549023076892</v>
+        <v>0.004467830061912537</v>
       </c>
       <c r="DZ6" t="n">
-        <v>0.000108575593912974</v>
+        <v>0.008556436747312546</v>
       </c>
       <c r="EA6" t="n">
-        <v>0.0005692500271834433</v>
+        <v>7.273745723068714e-05</v>
       </c>
       <c r="EB6" t="n">
-        <v>8.259275637101382e-05</v>
+        <v>0.003248807275667787</v>
       </c>
       <c r="EC6" t="n">
-        <v>6.885328730277251e-06</v>
+        <v>0.0009202002547681332</v>
       </c>
       <c r="ED6" t="n">
-        <v>0.0001451725693186745</v>
+        <v>0.01190082170069218</v>
       </c>
       <c r="EE6" t="n">
-        <v>9.447801858186722e-05</v>
+        <v>0.03831960260868073</v>
       </c>
       <c r="EF6" t="n">
-        <v>0.0002865852147806436</v>
+        <v>0.007347842678427696</v>
       </c>
       <c r="EG6" t="n">
-        <v>1.479475395171903e-05</v>
+        <v>0.01444865111261606</v>
       </c>
       <c r="EH6" t="n">
-        <v>9.903343016048893e-05</v>
+        <v>0.003821481950581074</v>
       </c>
       <c r="EI6" t="n">
-        <v>0.0002014910714933649</v>
+        <v>0.02168959192931652</v>
       </c>
       <c r="EJ6" t="n">
-        <v>0.000200173759367317</v>
+        <v>0.004352922085672617</v>
       </c>
       <c r="EK6" t="n">
-        <v>5.997424887027591e-05</v>
+        <v>0.005162985064089298</v>
       </c>
       <c r="EL6" t="n">
-        <v>0.0001947888522408903</v>
+        <v>0.004969248548150063</v>
       </c>
       <c r="EM6" t="n">
-        <v>9.726863027026411e-06</v>
+        <v>0.01739756390452385</v>
       </c>
       <c r="EN6" t="n">
-        <v>4.049968265462667e-05</v>
+        <v>0.003753413446247578</v>
       </c>
       <c r="EO6" t="n">
-        <v>0.0004036282189190388</v>
+        <v>0.008860379457473755</v>
       </c>
       <c r="EP6" t="n">
-        <v>4.351154530013446e-06</v>
+        <v>0.02523499354720116</v>
       </c>
       <c r="EQ6" t="n">
-        <v>3.54099647665862e-05</v>
+        <v>0.007082400843501091</v>
       </c>
       <c r="ER6" t="n">
-        <v>0.0001391411497024819</v>
+        <v>0.02245271764695644</v>
       </c>
       <c r="ES6" t="n">
-        <v>5.9308124036761e-05</v>
+        <v>0.04622391611337662</v>
       </c>
       <c r="ET6" t="n">
-        <v>0.0006215922767296433</v>
+        <v>0.01299383398145437</v>
       </c>
       <c r="EU6" t="n">
-        <v>3.354440195835195e-05</v>
+        <v>0.02457252144813538</v>
       </c>
       <c r="EV6" t="n">
-        <v>0.0004046606773044914</v>
+        <v>0.009871096350252628</v>
       </c>
       <c r="EW6" t="n">
-        <v>0.0001287963677896187</v>
+        <v>0.0002131804940290749</v>
       </c>
       <c r="EX6" t="n">
-        <v>6.592381396330893e-05</v>
+        <v>0.01058811321854591</v>
       </c>
       <c r="EY6" t="n">
-        <v>0.000241389891016297</v>
+        <v>0.0444653183221817</v>
       </c>
       <c r="EZ6" t="n">
-        <v>0.0001266420003958046</v>
+        <v>0.001584127894602716</v>
       </c>
       <c r="FA6" t="n">
-        <v>0.000261914829025045</v>
+        <v>0.006022511050105095</v>
       </c>
       <c r="FB6" t="n">
-        <v>0.0002124338643625379</v>
+        <v>0.005267594940960407</v>
       </c>
       <c r="FC6" t="n">
-        <v>0.0002987226180266589</v>
+        <v>0.006945718545466661</v>
       </c>
       <c r="FD6" t="n">
-        <v>9.495938138570637e-05</v>
+        <v>0.003559896722435951</v>
       </c>
       <c r="FE6" t="n">
-        <v>1.224349216499832e-05</v>
+        <v>0.0009641882497817278</v>
       </c>
       <c r="FF6" t="n">
-        <v>1.738113496685401e-05</v>
+        <v>0.007202658336609602</v>
       </c>
       <c r="FG6" t="n">
-        <v>0.0003129024116788059</v>
+        <v>0.02139357849955559</v>
       </c>
       <c r="FH6" t="n">
-        <v>0.0004739611758850515</v>
+        <v>0.02344091795384884</v>
       </c>
       <c r="FI6" t="n">
-        <v>0.0001939657231559977</v>
+        <v>0.005298004485666752</v>
       </c>
       <c r="FJ6" t="n">
-        <v>0.0001529532019048929</v>
+        <v>0.01964482292532921</v>
       </c>
       <c r="FK6" t="n">
-        <v>0.0001008928229566664</v>
+        <v>0.02145030349493027</v>
       </c>
       <c r="FL6" t="n">
-        <v>6.392660725396127e-05</v>
+        <v>0.02851592935621738</v>
       </c>
       <c r="FM6" t="n">
-        <v>5.883031917619519e-05</v>
+        <v>0.01198386028409004</v>
       </c>
       <c r="FN6" t="n">
-        <v>6.299900269368663e-05</v>
+        <v>0.03842839971184731</v>
       </c>
       <c r="FO6" t="n">
-        <v>0.0002869789605028927</v>
+        <v>0.02573059499263763</v>
       </c>
       <c r="FP6" t="n">
-        <v>0.0003723649133462459</v>
+        <v>0.0285947285592556</v>
       </c>
       <c r="FQ6" t="n">
-        <v>0.0003478361177258193</v>
+        <v>0.003856380935758352</v>
       </c>
       <c r="FR6" t="n">
-        <v>0.0006440583383664489</v>
+        <v>0.01030269917100668</v>
       </c>
       <c r="FS6" t="n">
-        <v>0.0004403206403367221</v>
+        <v>0.03285625949501991</v>
       </c>
       <c r="FT6" t="n">
-        <v>0.001073521212674677</v>
+        <v>0.03391337394714355</v>
       </c>
       <c r="FU6" t="n">
-        <v>0.0002537959371693432</v>
+        <v>0.03151470795273781</v>
       </c>
       <c r="FV6" t="n">
-        <v>2.870189200621098e-05</v>
+        <v>0.01484773121774197</v>
       </c>
       <c r="FW6" t="n">
-        <v>0.0002602071326691657</v>
+        <v>0.04446279257535934</v>
       </c>
       <c r="FX6" t="n">
-        <v>8.010807505343109e-05</v>
+        <v>0.006473056972026825</v>
       </c>
       <c r="FY6" t="n">
-        <v>6.900029256939888e-05</v>
+        <v>0.02574627660214901</v>
       </c>
       <c r="FZ6" t="n">
-        <v>0.0004929681890644133</v>
+        <v>0.03157409280538559</v>
       </c>
       <c r="GA6" t="n">
-        <v>0.0002792950836010277</v>
+        <v>0.01210855506360531</v>
       </c>
       <c r="GB6" t="n">
-        <v>0.0003089991223532706</v>
+        <v>0.004808390513062477</v>
       </c>
       <c r="GC6" t="n">
-        <v>0.0001516502525191754</v>
+        <v>0.005969501566141844</v>
       </c>
       <c r="GD6" t="n">
-        <v>0.0003285098064225167</v>
+        <v>0.01083729416131973</v>
       </c>
       <c r="GE6" t="n">
-        <v>0.0001798223966034129</v>
+        <v>0.01504619512706995</v>
       </c>
       <c r="GF6" t="n">
-        <v>0.0003822773287538439</v>
+        <v>0.02130776643753052</v>
       </c>
       <c r="GG6" t="n">
-        <v>9.592678543413058e-05</v>
+        <v>0.02328974381089211</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>0.0002748302358668298</v>
+        <v>0.002255841158330441</v>
       </c>
       <c r="B7" t="n">
-        <v>0.002547397511079907</v>
+        <v>0.01541935745626688</v>
       </c>
       <c r="C7" t="n">
-        <v>0.0001703799061942846</v>
+        <v>0.002870061434805393</v>
       </c>
       <c r="D7" t="n">
-        <v>0.001403443980962038</v>
+        <v>0.01236460916697979</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0004054593737237155</v>
+        <v>0.002525746822357178</v>
       </c>
       <c r="F7" t="n">
-        <v>0.0004623816639650613</v>
+        <v>0.01032101735472679</v>
       </c>
       <c r="G7" t="n">
-        <v>0.0001313626707997173</v>
+        <v>0.005915889050811529</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0001463842927478254</v>
+        <v>0.00637128809466958</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0002467159065417945</v>
+        <v>0.001289673615247011</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0004109618603251874</v>
+        <v>0.001861677272245288</v>
       </c>
       <c r="K7" t="n">
-        <v>0.001612748834304512</v>
+        <v>0.01547682099044323</v>
       </c>
       <c r="L7" t="n">
-        <v>0.0001579678355483338</v>
+        <v>0.005435079801827669</v>
       </c>
       <c r="M7" t="n">
-        <v>0.001530939480289817</v>
+        <v>0.01721873879432678</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0009870126377791166</v>
+        <v>0.00573737733066082</v>
       </c>
       <c r="O7" t="n">
-        <v>0.0008574908133596182</v>
+        <v>0.009139047935605049</v>
       </c>
       <c r="P7" t="n">
-        <v>0.0001553197944303975</v>
+        <v>0.007279175333678722</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.0001747326750773937</v>
+        <v>0.00197810004465282</v>
       </c>
       <c r="R7" t="n">
-        <v>5.738663458032534e-05</v>
+        <v>0.002028378425166011</v>
       </c>
       <c r="S7" t="n">
-        <v>7.354423723882064e-05</v>
+        <v>0.001225514337420464</v>
       </c>
       <c r="T7" t="n">
-        <v>0.0004177488735876977</v>
+        <v>0.0002712308778427541</v>
       </c>
       <c r="U7" t="n">
-        <v>0.00012911346857436</v>
+        <v>0.0008047719020396471</v>
       </c>
       <c r="V7" t="n">
-        <v>0.0003021442971657962</v>
+        <v>0.0001683842856436968</v>
       </c>
       <c r="W7" t="n">
-        <v>0.0001031862193485722</v>
+        <v>0.001766249071806669</v>
       </c>
       <c r="X7" t="n">
-        <v>0.000340048864018172</v>
+        <v>0.004370907787233591</v>
       </c>
       <c r="Y7" t="n">
-        <v>0.0002448626910336316</v>
+        <v>0.0007149713928811252</v>
       </c>
       <c r="Z7" t="n">
-        <v>4.172818080405705e-05</v>
+        <v>0.002964731305837631</v>
       </c>
       <c r="AA7" t="n">
-        <v>3.198256308678538e-05</v>
+        <v>0.002725289668887854</v>
       </c>
       <c r="AB7" t="n">
-        <v>0.0003140224143862724</v>
+        <v>0.001846602186560631</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.0004043196386191994</v>
+        <v>0.001842544646933675</v>
       </c>
       <c r="AD7" t="n">
-        <v>6.047466013114899e-05</v>
+        <v>0.00332117173820734</v>
       </c>
       <c r="AE7" t="n">
-        <v>5.629303996101953e-05</v>
+        <v>4.794984124600887e-05</v>
       </c>
       <c r="AF7" t="n">
-        <v>0.0002838277141563594</v>
+        <v>0.001167671754956245</v>
       </c>
       <c r="AG7" t="n">
-        <v>0.0001563641562825069</v>
+        <v>0.006781882606446743</v>
       </c>
       <c r="AH7" t="n">
-        <v>6.812818901380524e-05</v>
+        <v>0.000184999720659107</v>
       </c>
       <c r="AI7" t="n">
-        <v>7.452961290255189e-05</v>
+        <v>0.003758796956390142</v>
       </c>
       <c r="AJ7" t="n">
-        <v>5.230855094850995e-05</v>
+        <v>0.001535977935418487</v>
       </c>
       <c r="AK7" t="n">
-        <v>0.0001333984691882506</v>
+        <v>0.001203439780510962</v>
       </c>
       <c r="AL7" t="n">
-        <v>0.0002179658331442624</v>
+        <v>0.005255087278783321</v>
       </c>
       <c r="AM7" t="n">
-        <v>9.249550203094259e-05</v>
+        <v>0.003292635548859835</v>
       </c>
       <c r="AN7" t="n">
-        <v>0.0001481987128499895</v>
+        <v>0.002714191330596805</v>
       </c>
       <c r="AO7" t="n">
-        <v>0.0003214525931980461</v>
+        <v>0.001628172933124006</v>
       </c>
       <c r="AP7" t="n">
-        <v>0.000324996595736593</v>
+        <v>0.003353998996317387</v>
       </c>
       <c r="AQ7" t="n">
-        <v>9.583916835254058e-05</v>
+        <v>0.002316229976713657</v>
       </c>
       <c r="AR7" t="n">
-        <v>0.0001920928771141917</v>
+        <v>0.0007963227108120918</v>
       </c>
       <c r="AS7" t="n">
-        <v>9.861108264885843e-05</v>
+        <v>0.001164486282505095</v>
       </c>
       <c r="AT7" t="n">
-        <v>0.0003032128734048456</v>
+        <v>0.0005166075425222516</v>
       </c>
       <c r="AU7" t="n">
-        <v>0.002080778358504176</v>
+        <v>0.008458664640784264</v>
       </c>
       <c r="AV7" t="n">
-        <v>7.44086064514704e-05</v>
+        <v>0.003241422353312373</v>
       </c>
       <c r="AW7" t="n">
-        <v>0.0002035284123849124</v>
+        <v>0.00607185484841466</v>
       </c>
       <c r="AX7" t="n">
-        <v>0.0004159290692768991</v>
+        <v>0.01089680194854736</v>
       </c>
       <c r="AY7" t="n">
-        <v>0.0003127572417724878</v>
+        <v>0.007590173278003931</v>
       </c>
       <c r="AZ7" t="n">
-        <v>5.132034129928797e-05</v>
+        <v>0.0002183362958021462</v>
       </c>
       <c r="BA7" t="n">
-        <v>4.471073771128431e-05</v>
+        <v>6.123929051682353e-05</v>
       </c>
       <c r="BB7" t="n">
-        <v>7.8221557487268e-05</v>
+        <v>0.001201831735670567</v>
       </c>
       <c r="BC7" t="n">
-        <v>6.833046063547954e-05</v>
+        <v>0.001892966683954</v>
       </c>
       <c r="BD7" t="n">
-        <v>0.0004209967155475169</v>
+        <v>0.0002521185670047998</v>
       </c>
       <c r="BE7" t="n">
-        <v>0.0003943870542570949</v>
+        <v>0.002922344952821732</v>
       </c>
       <c r="BF7" t="n">
-        <v>0.0002906484878621995</v>
+        <v>0.0007758378051221371</v>
       </c>
       <c r="BG7" t="n">
-        <v>0.0008184651960618794</v>
+        <v>0.004299501422792673</v>
       </c>
       <c r="BH7" t="n">
-        <v>0.0006267077988013625</v>
+        <v>0.001583487959578633</v>
       </c>
       <c r="BI7" t="n">
-        <v>0.0003035395930055529</v>
+        <v>0.001737493672408164</v>
       </c>
       <c r="BJ7" t="n">
-        <v>0.0001676971296546981</v>
+        <v>0.003454908495768905</v>
       </c>
       <c r="BK7" t="n">
-        <v>3.701401874423027e-05</v>
+        <v>0.002083147177472711</v>
       </c>
       <c r="BL7" t="n">
-        <v>0.0004923455417156219</v>
+        <v>0.001012349501252174</v>
       </c>
       <c r="BM7" t="n">
-        <v>0.0005900162504985929</v>
+        <v>0.0002453652559779584</v>
       </c>
       <c r="BN7" t="n">
-        <v>0.000154618319356814</v>
+        <v>0.0002465260622557253</v>
       </c>
       <c r="BO7" t="n">
-        <v>0.0001677844120422378</v>
+        <v>0.002696733921766281</v>
       </c>
       <c r="BP7" t="n">
-        <v>0.0004450304550118744</v>
+        <v>0.0002119774871971458</v>
       </c>
       <c r="BQ7" t="n">
-        <v>0.0002770553110167384</v>
+        <v>0.0002480471157468855</v>
       </c>
       <c r="BR7" t="n">
-        <v>6.272280006669462e-05</v>
+        <v>0.000175911613041535</v>
       </c>
       <c r="BS7" t="n">
-        <v>0.0001001998607534915</v>
+        <v>0.001649646670557559</v>
       </c>
       <c r="BT7" t="n">
-        <v>0.0001672616053838283</v>
+        <v>0.0007677078247070312</v>
       </c>
       <c r="BU7" t="n">
-        <v>0.0002476332592777908</v>
+        <v>3.453352837823331e-05</v>
       </c>
       <c r="BV7" t="n">
-        <v>0.0009770285105332732</v>
+        <v>0.006196033209562302</v>
       </c>
       <c r="BW7" t="n">
-        <v>8.820476068649441e-05</v>
+        <v>0.001893482054583728</v>
       </c>
       <c r="BX7" t="n">
-        <v>0.0001465776877012104</v>
+        <v>0.006892938166856766</v>
       </c>
       <c r="BY7" t="n">
-        <v>0.0001006620732368901</v>
+        <v>0.002322780434042215</v>
       </c>
       <c r="BZ7" t="n">
-        <v>0.0006779050454497337</v>
+        <v>0.00530196912586689</v>
       </c>
       <c r="CA7" t="n">
-        <v>4.845811417908408e-05</v>
+        <v>0.001086573349311948</v>
       </c>
       <c r="CB7" t="n">
-        <v>8.206309576053172e-05</v>
+        <v>0.0004597897059284151</v>
       </c>
       <c r="CC7" t="n">
-        <v>4.653922223951668e-05</v>
+        <v>0.002324142260476947</v>
       </c>
       <c r="CD7" t="n">
-        <v>0.0002090247726300731</v>
+        <v>0.0003041637246496975</v>
       </c>
       <c r="CE7" t="n">
-        <v>0.0004236219101585448</v>
+        <v>0.005216012243181467</v>
       </c>
       <c r="CF7" t="n">
-        <v>0.0001028910919558257</v>
+        <v>0.0004322601307649165</v>
       </c>
       <c r="CG7" t="n">
-        <v>0.0001213825889863074</v>
+        <v>0.004708719439804554</v>
       </c>
       <c r="CH7" t="n">
-        <v>9.977674926631153e-05</v>
+        <v>0.0001546421262901276</v>
       </c>
       <c r="CI7" t="n">
-        <v>0.000164779179613106</v>
+        <v>0.002087467117235065</v>
       </c>
       <c r="CJ7" t="n">
-        <v>0.0001018253897200339</v>
+        <v>0.00048011977924034</v>
       </c>
       <c r="CK7" t="n">
-        <v>1.401911504217423e-05</v>
+        <v>0.001095100305974483</v>
       </c>
       <c r="CL7" t="n">
-        <v>3.84966770070605e-05</v>
+        <v>6.704984116367996e-05</v>
       </c>
       <c r="CM7" t="n">
-        <v>0.0003267147403676063</v>
+        <v>0.0006860315916128457</v>
       </c>
       <c r="CN7" t="n">
-        <v>0.0003472024400252849</v>
+        <v>0.002429073443636298</v>
       </c>
       <c r="CO7" t="n">
-        <v>0.0002116924442816526</v>
+        <v>0.006409160327166319</v>
       </c>
       <c r="CP7" t="n">
-        <v>0.0005713840946555138</v>
+        <v>0.007114757783710957</v>
       </c>
       <c r="CQ7" t="n">
-        <v>0.0003877149720210582</v>
+        <v>0.0006207182887010276</v>
       </c>
       <c r="CR7" t="n">
-        <v>0.0003562625788617879</v>
+        <v>0.002149170730262995</v>
       </c>
       <c r="CS7" t="n">
-        <v>0.0001181555126095191</v>
+        <v>0.001103709219023585</v>
       </c>
       <c r="CT7" t="n">
-        <v>0.0004298301937524229</v>
+        <v>0.001833907910622656</v>
       </c>
       <c r="CU7" t="n">
-        <v>2.742112519626971e-05</v>
+        <v>0.0007547460263594985</v>
       </c>
       <c r="CV7" t="n">
-        <v>0.0001989298471016809</v>
+        <v>0.0002131634100805968</v>
       </c>
       <c r="CW7" t="n">
-        <v>0.0003103481139987707</v>
+        <v>0.004997235722839832</v>
       </c>
       <c r="CX7" t="n">
-        <v>0.000133356312289834</v>
+        <v>0.001058126683346927</v>
       </c>
       <c r="CY7" t="n">
-        <v>0.0002390425797784701</v>
+        <v>0.005114393308758736</v>
       </c>
       <c r="CZ7" t="n">
-        <v>9.275949560105801e-05</v>
+        <v>0.001177488244138658</v>
       </c>
       <c r="DA7" t="n">
-        <v>0.0001657514658290893</v>
+        <v>0.002335058059543371</v>
       </c>
       <c r="DB7" t="n">
-        <v>8.799722127150744e-05</v>
+        <v>0.0007321126759052277</v>
       </c>
       <c r="DC7" t="n">
-        <v>1.128836447605863e-05</v>
+        <v>0.0009454293176531792</v>
       </c>
       <c r="DD7" t="n">
-        <v>1.293580135097727e-05</v>
+        <v>0.0003184325760230422</v>
       </c>
       <c r="DE7" t="n">
-        <v>0.0001048077247105539</v>
+        <v>0.0008665719069540501</v>
       </c>
       <c r="DF7" t="n">
-        <v>0.0003222417435608804</v>
+        <v>0.004556396976113319</v>
       </c>
       <c r="DG7" t="n">
-        <v>0.0001082506205420941</v>
+        <v>0.001137211453169584</v>
       </c>
       <c r="DH7" t="n">
-        <v>0.0002993476809933782</v>
+        <v>0.003620503935962915</v>
       </c>
       <c r="DI7" t="n">
-        <v>6.592812860617414e-05</v>
+        <v>0.0005572091322392225</v>
       </c>
       <c r="DJ7" t="n">
-        <v>0.0001307359052589163</v>
+        <v>0.009789395146071911</v>
       </c>
       <c r="DK7" t="n">
-        <v>0.0001295421534450725</v>
+        <v>0.001137500163167715</v>
       </c>
       <c r="DL7" t="n">
-        <v>0.0001193568605231121</v>
+        <v>0.00834841001778841</v>
       </c>
       <c r="DM7" t="n">
-        <v>0.0001504308165749535</v>
+        <v>0.003571323119103909</v>
       </c>
       <c r="DN7" t="n">
-        <v>0.000413961912272498</v>
+        <v>0.0003312558401376009</v>
       </c>
       <c r="DO7" t="n">
-        <v>0.0001392155099892989</v>
+        <v>0.002668745117262006</v>
       </c>
       <c r="DP7" t="n">
-        <v>0.0002148750791093335</v>
+        <v>0.0006522417534142733</v>
       </c>
       <c r="DQ7" t="n">
-        <v>0.0001163788328994997</v>
+        <v>0.001416771905496716</v>
       </c>
       <c r="DR7" t="n">
-        <v>0.0001362231123493984</v>
+        <v>9.947696526069194e-05</v>
       </c>
       <c r="DS7" t="n">
-        <v>0.0002766206162050366</v>
+        <v>0.001398368971422315</v>
       </c>
       <c r="DT7" t="n">
-        <v>5.073300781077705e-05</v>
+        <v>0.001855816459283233</v>
       </c>
       <c r="DU7" t="n">
-        <v>3.269760782131925e-05</v>
+        <v>0.003487753681838512</v>
       </c>
       <c r="DV7" t="n">
-        <v>3.635764005593956e-05</v>
+        <v>0.006788899190723896</v>
       </c>
       <c r="DW7" t="n">
-        <v>0.0001342328905593604</v>
+        <v>3.900815499946475e-06</v>
       </c>
       <c r="DX7" t="n">
-        <v>2.006975591939408e-05</v>
+        <v>0.0003930712700821459</v>
       </c>
       <c r="DY7" t="n">
-        <v>0.0002661793259903789</v>
+        <v>0.003392911516129971</v>
       </c>
       <c r="DZ7" t="n">
-        <v>0.0002023586857831106</v>
+        <v>0.001973224803805351</v>
       </c>
       <c r="EA7" t="n">
-        <v>0.0003639575734268874</v>
+        <v>0.0002693824062589556</v>
       </c>
       <c r="EB7" t="n">
-        <v>0.0002406978019280359</v>
+        <v>0.005146823357790709</v>
       </c>
       <c r="EC7" t="n">
-        <v>3.774567085201852e-05</v>
+        <v>0.000388209824450314</v>
       </c>
       <c r="ED7" t="n">
-        <v>7.373571133939549e-05</v>
+        <v>0.00738892424851656</v>
       </c>
       <c r="EE7" t="n">
-        <v>3.742543776752427e-05</v>
+        <v>0.007111895363777876</v>
       </c>
       <c r="EF7" t="n">
-        <v>0.0001445650414098054</v>
+        <v>0.002489044796675444</v>
       </c>
       <c r="EG7" t="n">
-        <v>0.0001787693181540817</v>
+        <v>0.00330287660472095</v>
       </c>
       <c r="EH7" t="n">
-        <v>3.418056076043285e-05</v>
+        <v>0.003123615635558963</v>
       </c>
       <c r="EI7" t="n">
-        <v>0.0001908242265926674</v>
+        <v>0.004358403384685516</v>
       </c>
       <c r="EJ7" t="n">
-        <v>8.088034519460052e-05</v>
+        <v>0.0008295620209537446</v>
       </c>
       <c r="EK7" t="n">
-        <v>0.0001165518478956074</v>
+        <v>0.001485119806602597</v>
       </c>
       <c r="EL7" t="n">
-        <v>0.0001081838709069416</v>
+        <v>0.0001936759217642248</v>
       </c>
       <c r="EM7" t="n">
-        <v>9.483816393185407e-05</v>
+        <v>0.0001340448507107794</v>
       </c>
       <c r="EN7" t="n">
-        <v>2.300156847923063e-05</v>
+        <v>0.000651078182272613</v>
       </c>
       <c r="EO7" t="n">
-        <v>0.0002000357198994607</v>
+        <v>0.001391404890455306</v>
       </c>
       <c r="EP7" t="n">
-        <v>0.0003076659049838781</v>
+        <v>0.00516553083434701</v>
       </c>
       <c r="EQ7" t="n">
-        <v>7.69775579101406e-05</v>
+        <v>0.0002280283952131867</v>
       </c>
       <c r="ER7" t="n">
-        <v>0.0002100988349411637</v>
+        <v>0.003948574885725975</v>
       </c>
       <c r="ES7" t="n">
-        <v>0.0001469350245315582</v>
+        <v>0.0009431236539967358</v>
       </c>
       <c r="ET7" t="n">
-        <v>0.0006649682181887329</v>
+        <v>0.0005866955034434795</v>
       </c>
       <c r="EU7" t="n">
-        <v>0.0001769728260114789</v>
+        <v>0.001582670025527477</v>
       </c>
       <c r="EV7" t="n">
-        <v>0.0001440543419448659</v>
+        <v>0.002123817102983594</v>
       </c>
       <c r="EW7" t="n">
-        <v>1.585323116159998e-05</v>
+        <v>0.003878544783219695</v>
       </c>
       <c r="EX7" t="n">
-        <v>0.0001379839377477765</v>
+        <v>0.0002040171821136028</v>
       </c>
       <c r="EY7" t="n">
-        <v>0.0003331944171804935</v>
+        <v>0.00559340650215745</v>
       </c>
       <c r="EZ7" t="n">
-        <v>3.579217445803806e-05</v>
+        <v>0.0005586445913650095</v>
       </c>
       <c r="FA7" t="n">
-        <v>0.0001774880947778001</v>
+        <v>0.005449917167425156</v>
       </c>
       <c r="FB7" t="n">
-        <v>5.815028998767957e-06</v>
+        <v>9.679469803813845e-05</v>
       </c>
       <c r="FC7" t="n">
-        <v>0.0002210429811384529</v>
+        <v>0.002247984288260341</v>
       </c>
       <c r="FD7" t="n">
-        <v>0.0001037084439303726</v>
+        <v>0.0008937643142417073</v>
       </c>
       <c r="FE7" t="n">
-        <v>1.438763320038561e-05</v>
+        <v>0.001393736689351499</v>
       </c>
       <c r="FF7" t="n">
-        <v>3.949560777982697e-05</v>
+        <v>0.001067422446794808</v>
       </c>
       <c r="FG7" t="n">
-        <v>8.7342421466019e-05</v>
+        <v>0.0002818879438564181</v>
       </c>
       <c r="FH7" t="n">
-        <v>0.0001138985317084007</v>
+        <v>0.002534310799092054</v>
       </c>
       <c r="FI7" t="n">
-        <v>1.992441502807196e-05</v>
+        <v>0.0001550178858451545</v>
       </c>
       <c r="FJ7" t="n">
-        <v>0.0002446250291541219</v>
+        <v>0.002828667405992746</v>
       </c>
       <c r="FK7" t="n">
-        <v>0.0001446434325771406</v>
+        <v>0.001111237797886133</v>
       </c>
       <c r="FL7" t="n">
-        <v>0.0001689123891992494</v>
+        <v>0.0002217037254013121</v>
       </c>
       <c r="FM7" t="n">
-        <v>4.797590372618288e-05</v>
+        <v>0.001094421138986945</v>
       </c>
       <c r="FN7" t="n">
-        <v>7.642380660399795e-05</v>
+        <v>0.0005373699823394418</v>
       </c>
       <c r="FO7" t="n">
-        <v>0.0001779026933945715</v>
+        <v>0.0008860478410497308</v>
       </c>
       <c r="FP7" t="n">
-        <v>2.406279236311093e-06</v>
+        <v>0.002771401777863503</v>
       </c>
       <c r="FQ7" t="n">
-        <v>0.0001677592081250623</v>
+        <v>0.005942357704043388</v>
       </c>
       <c r="FR7" t="n">
-        <v>3.1459941965295e-05</v>
+        <v>0.004199176095426083</v>
       </c>
       <c r="FS7" t="n">
-        <v>0.0004439508193172514</v>
+        <v>0.00494513101875782</v>
       </c>
       <c r="FT7" t="n">
-        <v>0.0003449786454439163</v>
+        <v>0.005264018662273884</v>
       </c>
       <c r="FU7" t="n">
-        <v>2.189039150835015e-05</v>
+        <v>0.00222104974091053</v>
       </c>
       <c r="FV7" t="n">
-        <v>8.636793063487858e-05</v>
+        <v>0.0001720126019790769</v>
       </c>
       <c r="FW7" t="n">
-        <v>7.758807623758912e-05</v>
+        <v>0.006231115199625492</v>
       </c>
       <c r="FX7" t="n">
-        <v>0.0001890100538730621</v>
+        <v>0.003419855842366815</v>
       </c>
       <c r="FY7" t="n">
-        <v>0.000284538371488452</v>
+        <v>0.001586303347721696</v>
       </c>
       <c r="FZ7" t="n">
-        <v>0.0002635422279126942</v>
+        <v>0.0006538300076499581</v>
       </c>
       <c r="GA7" t="n">
-        <v>1.717678787827026e-05</v>
+        <v>0.001760449376888573</v>
       </c>
       <c r="GB7" t="n">
-        <v>0.0001228266628459096</v>
+        <v>0.004755309782922268</v>
       </c>
       <c r="GC7" t="n">
-        <v>0.0001622803829377517</v>
+        <v>0.001089623430743814</v>
       </c>
       <c r="GD7" t="n">
-        <v>0.0002987290499731898</v>
+        <v>0.003494134172797203</v>
       </c>
       <c r="GE7" t="n">
-        <v>0.0004316896083764732</v>
+        <v>0.002731818240135908</v>
       </c>
       <c r="GF7" t="n">
-        <v>1.145674832514487e-05</v>
+        <v>0.002833810867741704</v>
       </c>
       <c r="GG7" t="n">
-        <v>7.54209904698655e-05</v>
+        <v>0.001777463709004223</v>
       </c>
     </row>
     <row r="8">
@@ -4982,2278 +4982,2278 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>2.238724206016229e-10</v>
+        <v>2.297121604044605e-08</v>
       </c>
       <c r="B9" t="n">
-        <v>4.064785452673192e-10</v>
+        <v>1.181600879363032e-07</v>
       </c>
       <c r="C9" t="n">
-        <v>1.019161491311316e-10</v>
+        <v>1.670080962412612e-08</v>
       </c>
       <c r="D9" t="n">
-        <v>1.441834207582815e-09</v>
+        <v>3.96367525468122e-08</v>
       </c>
       <c r="E9" t="n">
-        <v>2.359160089504542e-11</v>
+        <v>1.76045400479552e-08</v>
       </c>
       <c r="F9" t="n">
-        <v>1.497089258117867e-11</v>
+        <v>6.191784507336706e-08</v>
       </c>
       <c r="G9" t="n">
-        <v>3.496294573301917e-11</v>
+        <v>2.147088551396337e-08</v>
       </c>
       <c r="H9" t="n">
-        <v>1.016590422953101e-10</v>
+        <v>3.660974456920485e-08</v>
       </c>
       <c r="I9" t="n">
-        <v>2.203057181127122e-11</v>
+        <v>1.200343202611975e-08</v>
       </c>
       <c r="J9" t="n">
-        <v>3.693582939501283e-10</v>
+        <v>1.261905246963124e-08</v>
       </c>
       <c r="K9" t="n">
-        <v>2.646478314272116e-10</v>
+        <v>1.290091375949487e-07</v>
       </c>
       <c r="L9" t="n">
-        <v>1.118036496716712e-10</v>
+        <v>3.925839209273363e-08</v>
       </c>
       <c r="M9" t="n">
-        <v>6.487541615030068e-10</v>
+        <v>7.939313917404434e-08</v>
       </c>
       <c r="N9" t="n">
-        <v>8.176620491795461e-11</v>
+        <v>6.284691522751018e-08</v>
       </c>
       <c r="O9" t="n">
-        <v>4.328088998306612e-10</v>
+        <v>8.251059568920027e-08</v>
       </c>
       <c r="P9" t="n">
-        <v>2.015022315671189e-10</v>
+        <v>5.544004810786873e-09</v>
       </c>
       <c r="Q9" t="n">
-        <v>4.871831826847028e-10</v>
+        <v>1.120147530286886e-08</v>
       </c>
       <c r="R9" t="n">
-        <v>4.992349242338712e-11</v>
+        <v>3.130859482780579e-08</v>
       </c>
       <c r="S9" t="n">
-        <v>5.425655411062102e-11</v>
+        <v>5.721182194662333e-09</v>
       </c>
       <c r="T9" t="n">
-        <v>3.861958322581849e-11</v>
+        <v>6.999409496444287e-09</v>
       </c>
       <c r="U9" t="n">
-        <v>1.529500553987262e-10</v>
+        <v>3.144184290704288e-08</v>
       </c>
       <c r="V9" t="n">
-        <v>1.731405470384306e-11</v>
+        <v>3.040808493892655e-09</v>
       </c>
       <c r="W9" t="n">
-        <v>3.054681507741464e-10</v>
+        <v>1.181884812240241e-08</v>
       </c>
       <c r="X9" t="n">
-        <v>2.421347670977791e-11</v>
+        <v>1.578012565062181e-08</v>
       </c>
       <c r="Y9" t="n">
-        <v>5.216440057687066e-10</v>
+        <v>3.896489175758688e-08</v>
       </c>
       <c r="Z9" t="n">
-        <v>7.008049696111129e-11</v>
+        <v>2.259882236899102e-08</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.251605152325808e-10</v>
+        <v>5.383999912567106e-09</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.129977639235946e-10</v>
+        <v>1.503647428791055e-09</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.229192581053695e-10</v>
+        <v>1.93308142826254e-08</v>
       </c>
       <c r="AD9" t="n">
-        <v>4.756325541754869e-12</v>
+        <v>6.903691840420834e-09</v>
       </c>
       <c r="AE9" t="n">
-        <v>2.528587617067757e-10</v>
+        <v>4.595928260187065e-08</v>
       </c>
       <c r="AF9" t="n">
-        <v>2.449620506439487e-10</v>
+        <v>4.247316809369295e-08</v>
       </c>
       <c r="AG9" t="n">
-        <v>3.113678481714288e-10</v>
+        <v>5.690892734833142e-08</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.112255218482794e-10</v>
+        <v>8.92260487717067e-09</v>
       </c>
       <c r="AI9" t="n">
-        <v>1.64218499909552e-10</v>
+        <v>4.365118400073698e-08</v>
       </c>
       <c r="AJ9" t="n">
-        <v>7.923279393695637e-11</v>
+        <v>6.585796796798604e-09</v>
       </c>
       <c r="AK9" t="n">
-        <v>5.750042109120557e-11</v>
+        <v>6.53711573761484e-09</v>
       </c>
       <c r="AL9" t="n">
-        <v>1.63062771618705e-10</v>
+        <v>2.870781123931465e-08</v>
       </c>
       <c r="AM9" t="n">
-        <v>1.202702798464017e-10</v>
+        <v>3.097772349747174e-08</v>
       </c>
       <c r="AN9" t="n">
-        <v>9.675141937615095e-11</v>
+        <v>2.316925495904343e-08</v>
       </c>
       <c r="AO9" t="n">
-        <v>2.305072799302366e-10</v>
+        <v>7.682535496655873e-09</v>
       </c>
       <c r="AP9" t="n">
-        <v>1.913727926128317e-10</v>
+        <v>1.890747292065953e-08</v>
       </c>
       <c r="AQ9" t="n">
-        <v>1.972215168954961e-10</v>
+        <v>2.060670922787722e-08</v>
       </c>
       <c r="AR9" t="n">
-        <v>1.439199037722716e-10</v>
+        <v>5.352904786093404e-09</v>
       </c>
       <c r="AS9" t="n">
-        <v>1.510377517499606e-10</v>
+        <v>2.492629214145836e-09</v>
       </c>
       <c r="AT9" t="n">
-        <v>1.624360368435163e-13</v>
+        <v>4.081900151220452e-09</v>
       </c>
       <c r="AU9" t="n">
-        <v>9.391239869094292e-11</v>
+        <v>9.921647858845972e-08</v>
       </c>
       <c r="AV9" t="n">
-        <v>7.854413647256919e-11</v>
+        <v>5.103807865225463e-08</v>
       </c>
       <c r="AW9" t="n">
-        <v>7.198976970101967e-10</v>
+        <v>1.289435402895833e-08</v>
       </c>
       <c r="AX9" t="n">
-        <v>1.193430423929165e-11</v>
+        <v>9.570130998781678e-08</v>
       </c>
       <c r="AY9" t="n">
-        <v>7.129482421097677e-11</v>
+        <v>8.305546828069055e-08</v>
       </c>
       <c r="AZ9" t="n">
-        <v>1.736987498279774e-10</v>
+        <v>2.803939302964409e-10</v>
       </c>
       <c r="BA9" t="n">
-        <v>1.489469103610475e-10</v>
+        <v>8.763006320577915e-09</v>
       </c>
       <c r="BB9" t="n">
-        <v>3.67697261527411e-10</v>
+        <v>2.911191288035297e-10</v>
       </c>
       <c r="BC9" t="n">
-        <v>1.808582728024533e-10</v>
+        <v>1.496696100389272e-08</v>
       </c>
       <c r="BD9" t="n">
-        <v>6.493892923398192e-11</v>
+        <v>3.463770781308995e-08</v>
       </c>
       <c r="BE9" t="n">
-        <v>5.368290534324416e-11</v>
+        <v>1.513171810074709e-08</v>
       </c>
       <c r="BF9" t="n">
-        <v>8.957391772757006e-11</v>
+        <v>2.958880251924256e-09</v>
       </c>
       <c r="BG9" t="n">
-        <v>5.785472101393907e-11</v>
+        <v>6.574695987637824e-08</v>
       </c>
       <c r="BH9" t="n">
-        <v>7.848174887747916e-11</v>
+        <v>1.698506668645905e-09</v>
       </c>
       <c r="BI9" t="n">
-        <v>1.322219139732184e-10</v>
+        <v>9.331277084356771e-09</v>
       </c>
       <c r="BJ9" t="n">
-        <v>6.117622519674626e-10</v>
+        <v>4.376724760390971e-08</v>
       </c>
       <c r="BK9" t="n">
-        <v>1.371595545474058e-11</v>
+        <v>1.141583894082032e-08</v>
       </c>
       <c r="BL9" t="n">
-        <v>4.502867523292764e-11</v>
+        <v>7.449107997103965e-11</v>
       </c>
       <c r="BM9" t="n">
-        <v>1.494273177415906e-10</v>
+        <v>9.319482074943153e-09</v>
       </c>
       <c r="BN9" t="n">
-        <v>1.160540205602523e-10</v>
+        <v>1.674407101859288e-08</v>
       </c>
       <c r="BO9" t="n">
-        <v>1.269455651708995e-10</v>
+        <v>8.736348533489036e-09</v>
       </c>
       <c r="BP9" t="n">
-        <v>1.98562971620575e-10</v>
+        <v>3.297253670098144e-08</v>
       </c>
       <c r="BQ9" t="n">
-        <v>2.114009245435255e-10</v>
+        <v>1.274256478112079e-09</v>
       </c>
       <c r="BR9" t="n">
-        <v>2.013994873650837e-11</v>
+        <v>1.41734428638074e-08</v>
       </c>
       <c r="BS9" t="n">
-        <v>2.540762392144735e-11</v>
+        <v>1.697279294887721e-08</v>
       </c>
       <c r="BT9" t="n">
-        <v>6.686087794527396e-11</v>
+        <v>1.455730203048233e-09</v>
       </c>
       <c r="BU9" t="n">
-        <v>3.134329601417463e-12</v>
+        <v>1.277464711790799e-08</v>
       </c>
       <c r="BV9" t="n">
-        <v>7.164693144323664e-11</v>
+        <v>6.515632833270502e-08</v>
       </c>
       <c r="BW9" t="n">
-        <v>8.757133213022072e-11</v>
+        <v>3.362570311082891e-08</v>
       </c>
       <c r="BX9" t="n">
-        <v>2.791622211173461e-10</v>
+        <v>9.230307185248421e-09</v>
       </c>
       <c r="BY9" t="n">
-        <v>1.712552044619287e-10</v>
+        <v>2.049989733521329e-09</v>
       </c>
       <c r="BZ9" t="n">
-        <v>1.861306664352469e-10</v>
+        <v>3.90728978061361e-08</v>
       </c>
       <c r="CA9" t="n">
-        <v>2.309528956967455e-10</v>
+        <v>3.575469875727322e-08</v>
       </c>
       <c r="CB9" t="n">
-        <v>1.371311536546571e-10</v>
+        <v>6.577472344559965e-09</v>
       </c>
       <c r="CC9" t="n">
-        <v>2.469724424969399e-10</v>
+        <v>1.257059167869556e-08</v>
       </c>
       <c r="CD9" t="n">
-        <v>2.625549777590663e-11</v>
+        <v>5.538611236310942e-10</v>
       </c>
       <c r="CE9" t="n">
-        <v>7.269754243033333e-11</v>
+        <v>4.218581750592421e-08</v>
       </c>
       <c r="CF9" t="n">
-        <v>1.57546115042706e-10</v>
+        <v>3.833712014511548e-09</v>
       </c>
       <c r="CG9" t="n">
-        <v>1.452200443230467e-10</v>
+        <v>1.385848413804069e-08</v>
       </c>
       <c r="CH9" t="n">
-        <v>7.866551854363024e-11</v>
+        <v>1.545373073952305e-08</v>
       </c>
       <c r="CI9" t="n">
-        <v>1.686658451793832e-11</v>
+        <v>1.525211246189428e-08</v>
       </c>
       <c r="CJ9" t="n">
-        <v>8.800968287481226e-11</v>
+        <v>7.882225538935472e-09</v>
       </c>
       <c r="CK9" t="n">
-        <v>6.457055029551739e-11</v>
+        <v>4.309247403355698e-10</v>
       </c>
       <c r="CL9" t="n">
-        <v>1.853548980967901e-10</v>
+        <v>7.796878698229648e-10</v>
       </c>
       <c r="CM9" t="n">
-        <v>1.331854071473515e-11</v>
+        <v>5.017333037926619e-08</v>
       </c>
       <c r="CN9" t="n">
-        <v>3.159635331151378e-10</v>
+        <v>7.227616549698723e-08</v>
       </c>
       <c r="CO9" t="n">
-        <v>5.934079616576327e-11</v>
+        <v>6.356316362143843e-08</v>
       </c>
       <c r="CP9" t="n">
-        <v>3.435401685347728e-10</v>
+        <v>1.277429539925379e-08</v>
       </c>
       <c r="CQ9" t="n">
-        <v>1.73475289688696e-10</v>
+        <v>1.473847177635434e-08</v>
       </c>
       <c r="CR9" t="n">
-        <v>2.851165414874401e-10</v>
+        <v>2.399770160366188e-08</v>
       </c>
       <c r="CS9" t="n">
-        <v>1.81344703142905e-10</v>
+        <v>3.379483715093556e-08</v>
       </c>
       <c r="CT9" t="n">
-        <v>5.142962167248299e-10</v>
+        <v>1.823296402747587e-09</v>
       </c>
       <c r="CU9" t="n">
-        <v>1.122539474568418e-11</v>
+        <v>3.904634837681442e-09</v>
       </c>
       <c r="CV9" t="n">
-        <v>3.385300373359712e-11</v>
+        <v>1.346560862813817e-09</v>
       </c>
       <c r="CW9" t="n">
-        <v>8.184809774380852e-11</v>
+        <v>3.681608973238326e-08</v>
       </c>
       <c r="CX9" t="n">
-        <v>9.000437894979285e-11</v>
+        <v>3.650109769992582e-09</v>
       </c>
       <c r="CY9" t="n">
-        <v>2.556513056806153e-10</v>
+        <v>1.870391486136214e-08</v>
       </c>
       <c r="CZ9" t="n">
-        <v>8.569791404289262e-11</v>
+        <v>2.313441704870911e-08</v>
       </c>
       <c r="DA9" t="n">
-        <v>4.596926311828398e-11</v>
+        <v>1.48527465881898e-08</v>
       </c>
       <c r="DB9" t="n">
-        <v>8.135903062367333e-11</v>
+        <v>1.153863848912806e-08</v>
       </c>
       <c r="DC9" t="n">
-        <v>7.610761326715121e-11</v>
+        <v>2.115089436927065e-09</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.384275333249363e-10</v>
+        <v>3.118997726758721e-09</v>
       </c>
       <c r="DE9" t="n">
-        <v>7.995514667014092e-11</v>
+        <v>1.763853951786132e-08</v>
       </c>
       <c r="DF9" t="n">
-        <v>2.897481421459958e-10</v>
+        <v>1.38649092207288e-09</v>
       </c>
       <c r="DG9" t="n">
-        <v>5.576450412547729e-10</v>
+        <v>1.808064808983545e-09</v>
       </c>
       <c r="DH9" t="n">
-        <v>1.209518929456976e-09</v>
+        <v>1.638664848258031e-08</v>
       </c>
       <c r="DI9" t="n">
-        <v>4.526544972183189e-10</v>
+        <v>3.808171111785441e-09</v>
       </c>
       <c r="DJ9" t="n">
-        <v>4.620236832009184e-11</v>
+        <v>5.15421945124217e-08</v>
       </c>
       <c r="DK9" t="n">
-        <v>9.596962807778553e-11</v>
+        <v>7.02762559257053e-09</v>
       </c>
       <c r="DL9" t="n">
-        <v>7.391549039503786e-10</v>
+        <v>5.768212218981716e-08</v>
       </c>
       <c r="DM9" t="n">
-        <v>6.795578683105319e-11</v>
+        <v>1.177060848789324e-08</v>
       </c>
       <c r="DN9" t="n">
-        <v>5.808499514703414e-11</v>
+        <v>1.366709412309319e-08</v>
       </c>
       <c r="DO9" t="n">
-        <v>4.504610573441425e-11</v>
+        <v>2.640511098661591e-08</v>
       </c>
       <c r="DP9" t="n">
-        <v>2.338699511827969e-10</v>
+        <v>3.451958718869719e-10</v>
       </c>
       <c r="DQ9" t="n">
-        <v>1.280833425432171e-11</v>
+        <v>1.598704280070251e-08</v>
       </c>
       <c r="DR9" t="n">
-        <v>1.948538969065439e-10</v>
+        <v>1.505868318929515e-08</v>
       </c>
       <c r="DS9" t="n">
-        <v>1.71001934834436e-10</v>
+        <v>1.331774335255886e-08</v>
       </c>
       <c r="DT9" t="n">
-        <v>3.349696908738764e-11</v>
+        <v>3.11014076714855e-08</v>
       </c>
       <c r="DU9" t="n">
-        <v>5.801633479185497e-11</v>
+        <v>3.217256683285541e-09</v>
       </c>
       <c r="DV9" t="n">
-        <v>3.930044900624097e-10</v>
+        <v>7.373925914322399e-09</v>
       </c>
       <c r="DW9" t="n">
-        <v>1.089625820127615e-10</v>
+        <v>4.213491777704803e-10</v>
       </c>
       <c r="DX9" t="n">
-        <v>1.155497503235736e-10</v>
+        <v>2.207853988522857e-08</v>
       </c>
       <c r="DY9" t="n">
-        <v>2.468289739265828e-10</v>
+        <v>2.65623985029606e-08</v>
       </c>
       <c r="DZ9" t="n">
-        <v>6.432517712928743e-11</v>
+        <v>2.524967790407118e-09</v>
       </c>
       <c r="EA9" t="n">
-        <v>2.000291182691072e-10</v>
+        <v>4.790078733662995e-08</v>
       </c>
       <c r="EB9" t="n">
-        <v>3.566660577991598e-10</v>
+        <v>1.580386133070988e-08</v>
       </c>
       <c r="EC9" t="n">
-        <v>7.854650263539042e-11</v>
+        <v>2.622453143530379e-09</v>
       </c>
       <c r="ED9" t="n">
-        <v>6.313695399828845e-11</v>
+        <v>3.357974165396627e-08</v>
       </c>
       <c r="EE9" t="n">
-        <v>1.630638332694723e-11</v>
+        <v>5.614069564785495e-08</v>
       </c>
       <c r="EF9" t="n">
-        <v>1.901305501927908e-12</v>
+        <v>2.310362123836285e-09</v>
       </c>
       <c r="EG9" t="n">
-        <v>4.601710679175142e-11</v>
+        <v>1.388066106500219e-09</v>
       </c>
       <c r="EH9" t="n">
-        <v>8.582990221328579e-12</v>
+        <v>2.426750178585735e-08</v>
       </c>
       <c r="EI9" t="n">
-        <v>1.54232238092078e-10</v>
+        <v>1.463129173373545e-08</v>
       </c>
       <c r="EJ9" t="n">
-        <v>9.941372725030817e-11</v>
+        <v>1.78327237421172e-08</v>
       </c>
       <c r="EK9" t="n">
-        <v>6.478276248778059e-11</v>
+        <v>1.3588763891903e-08</v>
       </c>
       <c r="EL9" t="n">
-        <v>1.2550940842182e-10</v>
+        <v>1.547002526081087e-08</v>
       </c>
       <c r="EM9" t="n">
-        <v>1.753716616370582e-11</v>
+        <v>3.761701616866731e-09</v>
       </c>
       <c r="EN9" t="n">
-        <v>1.083606676610671e-10</v>
+        <v>1.711897468226198e-08</v>
       </c>
       <c r="EO9" t="n">
-        <v>3.199207565529605e-11</v>
+        <v>7.044084426865993e-09</v>
       </c>
       <c r="EP9" t="n">
-        <v>1.347553735264739e-10</v>
+        <v>3.366347911537559e-08</v>
       </c>
       <c r="EQ9" t="n">
-        <v>1.687335687838853e-10</v>
+        <v>1.170955954421515e-08</v>
       </c>
       <c r="ER9" t="n">
-        <v>4.319289717558128e-12</v>
+        <v>8.363512105091786e-10</v>
       </c>
       <c r="ES9" t="n">
-        <v>3.965485995127693e-10</v>
+        <v>2.528432929693736e-08</v>
       </c>
       <c r="ET9" t="n">
-        <v>5.028782251725872e-11</v>
+        <v>8.701894316232028e-09</v>
       </c>
       <c r="EU9" t="n">
-        <v>9.230324837794512e-12</v>
+        <v>3.042404106423646e-09</v>
       </c>
       <c r="EV9" t="n">
-        <v>3.834980388806031e-10</v>
+        <v>1.157940054952178e-08</v>
       </c>
       <c r="EW9" t="n">
-        <v>8.95196416994537e-11</v>
+        <v>2.098400031513847e-08</v>
       </c>
       <c r="EX9" t="n">
-        <v>1.58780766312816e-11</v>
+        <v>4.405727449530161e-10</v>
       </c>
       <c r="EY9" t="n">
-        <v>6.294596788247731e-11</v>
+        <v>4.125597641291279e-08</v>
       </c>
       <c r="EZ9" t="n">
-        <v>1.293141843605738e-10</v>
+        <v>1.175060271307871e-09</v>
       </c>
       <c r="FA9" t="n">
-        <v>2.060972226214375e-10</v>
+        <v>1.717780051535556e-08</v>
       </c>
       <c r="FB9" t="n">
-        <v>5.565567451348841e-11</v>
+        <v>1.0658578020184e-08</v>
       </c>
       <c r="FC9" t="n">
-        <v>2.200677834407472e-11</v>
+        <v>1.227747592480455e-08</v>
       </c>
       <c r="FD9" t="n">
-        <v>9.776033454977906e-11</v>
+        <v>8.70798988472643e-11</v>
       </c>
       <c r="FE9" t="n">
-        <v>6.38051417256591e-11</v>
+        <v>2.964678280648059e-09</v>
       </c>
       <c r="FF9" t="n">
-        <v>1.841106156419414e-10</v>
+        <v>1.095579627019561e-08</v>
       </c>
       <c r="FG9" t="n">
-        <v>6.99423366445906e-11</v>
+        <v>1.423000028921706e-08</v>
       </c>
       <c r="FH9" t="n">
-        <v>1.691248391333389e-10</v>
+        <v>8.347751823123417e-09</v>
       </c>
       <c r="FI9" t="n">
-        <v>3.527108050072059e-10</v>
+        <v>1.599128829354868e-08</v>
       </c>
       <c r="FJ9" t="n">
-        <v>3.986361241103964e-10</v>
+        <v>1.580811925805392e-08</v>
       </c>
       <c r="FK9" t="n">
-        <v>1.963746526500998e-10</v>
+        <v>2.2677395516979e-09</v>
       </c>
       <c r="FL9" t="n">
-        <v>3.48845084763294e-11</v>
+        <v>1.364838375650379e-08</v>
       </c>
       <c r="FM9" t="n">
-        <v>2.205799293220068e-10</v>
+        <v>1.472126509582949e-08</v>
       </c>
       <c r="FN9" t="n">
-        <v>1.605411498184495e-10</v>
+        <v>1.14510765314435e-08</v>
       </c>
       <c r="FO9" t="n">
-        <v>4.670131295569924e-11</v>
+        <v>5.39044862080118e-08</v>
       </c>
       <c r="FP9" t="n">
-        <v>4.187921537335271e-11</v>
+        <v>3.350176669414395e-08</v>
       </c>
       <c r="FQ9" t="n">
-        <v>5.152882981418472e-11</v>
+        <v>4.981421497518568e-08</v>
       </c>
       <c r="FR9" t="n">
-        <v>3.065554060599496e-11</v>
+        <v>3.057807873574347e-08</v>
       </c>
       <c r="FS9" t="n">
-        <v>6.828856924379068e-12</v>
+        <v>2.081159600209048e-08</v>
       </c>
       <c r="FT9" t="n">
-        <v>1.848987629671228e-10</v>
+        <v>5.932314195433719e-08</v>
       </c>
       <c r="FU9" t="n">
-        <v>9.947792589670712e-12</v>
+        <v>3.969169881656853e-08</v>
       </c>
       <c r="FV9" t="n">
-        <v>1.301484961468979e-13</v>
+        <v>3.187168218232728e-08</v>
       </c>
       <c r="FW9" t="n">
-        <v>1.293096324461729e-10</v>
+        <v>4.050915691777845e-08</v>
       </c>
       <c r="FX9" t="n">
-        <v>2.645821409186233e-11</v>
+        <v>7.127479939583736e-09</v>
       </c>
       <c r="FY9" t="n">
-        <v>2.576184543467974e-10</v>
+        <v>9.930263278334905e-10</v>
       </c>
       <c r="FZ9" t="n">
-        <v>1.784262182447094e-10</v>
+        <v>2.615841765418736e-09</v>
       </c>
       <c r="GA9" t="n">
-        <v>3.064268977448492e-11</v>
+        <v>2.198853366053299e-08</v>
       </c>
       <c r="GB9" t="n">
-        <v>3.635147391434224e-11</v>
+        <v>2.174359536866177e-08</v>
       </c>
       <c r="GC9" t="n">
-        <v>2.269127385989833e-10</v>
+        <v>1.98906562332013e-08</v>
       </c>
       <c r="GD9" t="n">
-        <v>4.266691167043035e-11</v>
+        <v>3.842909990225962e-08</v>
       </c>
       <c r="GE9" t="n">
-        <v>5.567897809477529e-10</v>
+        <v>4.669448472327531e-08</v>
       </c>
       <c r="GF9" t="n">
-        <v>1.510939429127944e-10</v>
+        <v>1.908758484603368e-09</v>
       </c>
       <c r="GG9" t="n">
-        <v>3.0107388804268e-10</v>
+        <v>2.459009351696295e-08</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>0.0005531011847779155</v>
+        <v>0.008366726338863373</v>
       </c>
       <c r="B10" t="n">
-        <v>0.00362528907135129</v>
+        <v>0.04433266073465347</v>
       </c>
       <c r="C10" t="n">
-        <v>0.0001047136101988144</v>
+        <v>0.0476982481777668</v>
       </c>
       <c r="D10" t="n">
-        <v>0.00191434274893254</v>
+        <v>0.01346485782414675</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0003132206620648503</v>
+        <v>0.02974815666675568</v>
       </c>
       <c r="F10" t="n">
-        <v>0.003196629928424954</v>
+        <v>0.05323534086346626</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0002103058941429481</v>
+        <v>0.01268789079040289</v>
       </c>
       <c r="H10" t="n">
-        <v>0.0008186909253709018</v>
+        <v>0.04924879223108292</v>
       </c>
       <c r="I10" t="n">
-        <v>0.000183352647582069</v>
+        <v>0.00356050580739975</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0008261582115665078</v>
+        <v>0.01436241623014212</v>
       </c>
       <c r="K10" t="n">
-        <v>0.00299414386972785</v>
+        <v>0.1260486841201782</v>
       </c>
       <c r="L10" t="n">
-        <v>0.0002044920984189957</v>
+        <v>0.04004011675715446</v>
       </c>
       <c r="M10" t="n">
-        <v>0.001925593474879861</v>
+        <v>0.01024734321981668</v>
       </c>
       <c r="N10" t="n">
-        <v>0.0004485188110265881</v>
+        <v>0.04936583340167999</v>
       </c>
       <c r="O10" t="n">
-        <v>0.00331336073577404</v>
+        <v>0.07832098007202148</v>
       </c>
       <c r="P10" t="n">
-        <v>0.0003670458972919732</v>
+        <v>0.04840818047523499</v>
       </c>
       <c r="Q10" t="n">
-        <v>9.335152572020888e-05</v>
+        <v>0.003273181151598692</v>
       </c>
       <c r="R10" t="n">
-        <v>0.0001155285281129181</v>
+        <v>0.005972533952444792</v>
       </c>
       <c r="S10" t="n">
-        <v>0.0002302873908774927</v>
+        <v>0.01512652728706598</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0005460306419990957</v>
+        <v>7.346458733081818e-05</v>
       </c>
       <c r="U10" t="n">
-        <v>7.52300547901541e-06</v>
+        <v>0.001280649099498987</v>
       </c>
       <c r="V10" t="n">
-        <v>0.0005089603364467621</v>
+        <v>0.02974164858460426</v>
       </c>
       <c r="W10" t="n">
-        <v>0.0001060158392647281</v>
+        <v>0.03477873653173447</v>
       </c>
       <c r="X10" t="n">
-        <v>6.320312240859494e-05</v>
+        <v>0.01455342769622803</v>
       </c>
       <c r="Y10" t="n">
-        <v>0.0002867936855182052</v>
+        <v>0.01400715950876474</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.644621079321951e-05</v>
+        <v>0.04713165387511253</v>
       </c>
       <c r="AA10" t="n">
-        <v>0.0003982579510193318</v>
+        <v>0.01479696948081255</v>
       </c>
       <c r="AB10" t="n">
-        <v>7.766272756271064e-05</v>
+        <v>0.04481573402881622</v>
       </c>
       <c r="AC10" t="n">
-        <v>0.0003180743951816112</v>
+        <v>0.001738655846565962</v>
       </c>
       <c r="AD10" t="n">
-        <v>0.0002167767088394612</v>
+        <v>0.01417894847691059</v>
       </c>
       <c r="AE10" t="n">
-        <v>0.0004399904864840209</v>
+        <v>0.002252937061712146</v>
       </c>
       <c r="AF10" t="n">
-        <v>0.000195693937712349</v>
+        <v>0.06862040609121323</v>
       </c>
       <c r="AG10" t="n">
-        <v>0.0001128786025219597</v>
+        <v>0.01357302535325289</v>
       </c>
       <c r="AH10" t="n">
-        <v>0.0007012803107500076</v>
+        <v>0.02626373991370201</v>
       </c>
       <c r="AI10" t="n">
-        <v>0.0001834112190408632</v>
+        <v>0.05023852363228798</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0.0002217896108049899</v>
+        <v>0.007149365730583668</v>
       </c>
       <c r="AK10" t="n">
-        <v>0.0004067622940056026</v>
+        <v>0.01256846077740192</v>
       </c>
       <c r="AL10" t="n">
-        <v>0.000575434707570821</v>
+        <v>0.000909857451915741</v>
       </c>
       <c r="AM10" t="n">
-        <v>0.0001489442074671388</v>
+        <v>0.003399191424250603</v>
       </c>
       <c r="AN10" t="n">
-        <v>8.208758663386106e-05</v>
+        <v>0.0101805878803134</v>
       </c>
       <c r="AO10" t="n">
-        <v>7.780576561344787e-05</v>
+        <v>0.02700704149901867</v>
       </c>
       <c r="AP10" t="n">
-        <v>0.0004946758272126317</v>
+        <v>0.001568440464325249</v>
       </c>
       <c r="AQ10" t="n">
-        <v>0.0002220882452093065</v>
+        <v>0.01626927219331264</v>
       </c>
       <c r="AR10" t="n">
-        <v>1.30567786982283e-06</v>
+        <v>0.0413389690220356</v>
       </c>
       <c r="AS10" t="n">
-        <v>0.0003692434402182698</v>
+        <v>0.004623338580131531</v>
       </c>
       <c r="AT10" t="n">
-        <v>0.0005135845276527107</v>
+        <v>0.005087803117930889</v>
       </c>
       <c r="AU10" t="n">
-        <v>0.002721202559769154</v>
+        <v>0.1191699877381325</v>
       </c>
       <c r="AV10" t="n">
-        <v>0.0003084950731135905</v>
+        <v>0.0268159918487072</v>
       </c>
       <c r="AW10" t="n">
-        <v>0.0003858261043205857</v>
+        <v>0.008245257660746574</v>
       </c>
       <c r="AX10" t="n">
-        <v>0.0007401896291412413</v>
+        <v>0.03210487216711044</v>
       </c>
       <c r="AY10" t="n">
-        <v>0.001625556615181267</v>
+        <v>0.05976209416985512</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.000391719862818718</v>
+        <v>0.00888175331056118</v>
       </c>
       <c r="BA10" t="n">
-        <v>0.0007004695944488049</v>
+        <v>0.01516449078917503</v>
       </c>
       <c r="BB10" t="n">
-        <v>0.0004734638496302068</v>
+        <v>0.005992304533720016</v>
       </c>
       <c r="BC10" t="n">
-        <v>0.000381037563784048</v>
+        <v>0.02340552024543285</v>
       </c>
       <c r="BD10" t="n">
-        <v>0.0007167697185650468</v>
+        <v>0.01554835215210915</v>
       </c>
       <c r="BE10" t="n">
-        <v>0.0008419638616032898</v>
+        <v>0.001112384721636772</v>
       </c>
       <c r="BF10" t="n">
-        <v>0.0009401847491972148</v>
+        <v>0.0211401954293251</v>
       </c>
       <c r="BG10" t="n">
-        <v>0.001193784293718636</v>
+        <v>0.02447527460753918</v>
       </c>
       <c r="BH10" t="n">
-        <v>0.001184621476568282</v>
+        <v>0.01351162418723106</v>
       </c>
       <c r="BI10" t="n">
-        <v>8.501033880747855e-05</v>
+        <v>0.01590888202190399</v>
       </c>
       <c r="BJ10" t="n">
-        <v>0.0007418434252031147</v>
+        <v>0.05025136098265648</v>
       </c>
       <c r="BK10" t="n">
-        <v>5.524299194803461e-05</v>
+        <v>0.01855229213833809</v>
       </c>
       <c r="BL10" t="n">
-        <v>0.0002392902242718264</v>
+        <v>0.01904138177633286</v>
       </c>
       <c r="BM10" t="n">
-        <v>0.0008573115337640047</v>
+        <v>0.05475518107414246</v>
       </c>
       <c r="BN10" t="n">
-        <v>0.0002665160282049328</v>
+        <v>0.004878135863691568</v>
       </c>
       <c r="BO10" t="n">
-        <v>0.0008197749266400933</v>
+        <v>0.02319318801164627</v>
       </c>
       <c r="BP10" t="n">
-        <v>0.000655703479424119</v>
+        <v>0.03176965937018394</v>
       </c>
       <c r="BQ10" t="n">
-        <v>2.018147461058106e-05</v>
+        <v>0.0007944523822516203</v>
       </c>
       <c r="BR10" t="n">
-        <v>0.0005778798367828131</v>
+        <v>0.01192890293896198</v>
       </c>
       <c r="BS10" t="n">
-        <v>9.705962293082848e-05</v>
+        <v>0.02848970517516136</v>
       </c>
       <c r="BT10" t="n">
-        <v>5.335832975106314e-05</v>
+        <v>0.0005109596531838179</v>
       </c>
       <c r="BU10" t="n">
-        <v>0.0002534226223360747</v>
+        <v>0.008558966219425201</v>
       </c>
       <c r="BV10" t="n">
-        <v>0.001366663258522749</v>
+        <v>0.05616727843880653</v>
       </c>
       <c r="BW10" t="n">
-        <v>2.916247467510402e-05</v>
+        <v>0.01216430217027664</v>
       </c>
       <c r="BX10" t="n">
-        <v>0.0001222840946866199</v>
+        <v>0.03631526231765747</v>
       </c>
       <c r="BY10" t="n">
-        <v>0.0001342854666290805</v>
+        <v>0.02474358677864075</v>
       </c>
       <c r="BZ10" t="n">
-        <v>0.0003008756320923567</v>
+        <v>0.0203249491751194</v>
       </c>
       <c r="CA10" t="n">
-        <v>0.000566161994356662</v>
+        <v>0.009898615069687366</v>
       </c>
       <c r="CB10" t="n">
-        <v>0.0004038803454022855</v>
+        <v>0.02507880143821239</v>
       </c>
       <c r="CC10" t="n">
-        <v>0.0003759682876989245</v>
+        <v>0.0001810017856769264</v>
       </c>
       <c r="CD10" t="n">
-        <v>8.368556154891849e-05</v>
+        <v>0.01441378518939018</v>
       </c>
       <c r="CE10" t="n">
-        <v>0.0006943652988411486</v>
+        <v>0.01546125765889883</v>
       </c>
       <c r="CF10" t="n">
-        <v>0.000294652912998572</v>
+        <v>0.01357083488255739</v>
       </c>
       <c r="CG10" t="n">
-        <v>0.0004306017654016614</v>
+        <v>0.0003348815080244094</v>
       </c>
       <c r="CH10" t="n">
-        <v>0.0002177262504119426</v>
+        <v>0.01609377004206181</v>
       </c>
       <c r="CI10" t="n">
-        <v>0.0005384949618019164</v>
+        <v>0.02170893549919128</v>
       </c>
       <c r="CJ10" t="n">
-        <v>0.0001834806462284178</v>
+        <v>0.009508880786597729</v>
       </c>
       <c r="CK10" t="n">
-        <v>6.932466203579679e-05</v>
+        <v>0.004723732359707355</v>
       </c>
       <c r="CL10" t="n">
-        <v>0.0002168817009078339</v>
+        <v>0.004605364985764027</v>
       </c>
       <c r="CM10" t="n">
-        <v>0.00052851956570521</v>
+        <v>0.001436576247215271</v>
       </c>
       <c r="CN10" t="n">
-        <v>0.0004568486474454403</v>
+        <v>0.07091566920280457</v>
       </c>
       <c r="CO10" t="n">
-        <v>7.852971612010151e-05</v>
+        <v>0.006290078163146973</v>
       </c>
       <c r="CP10" t="n">
-        <v>0.0005005650455132127</v>
+        <v>0.05186638236045837</v>
       </c>
       <c r="CQ10" t="n">
-        <v>0.0002011025790125132</v>
+        <v>0.02743317931890488</v>
       </c>
       <c r="CR10" t="n">
-        <v>0.0001335072593064979</v>
+        <v>0.0258591752499342</v>
       </c>
       <c r="CS10" t="n">
-        <v>0.0002063280699076131</v>
+        <v>0.02448279038071632</v>
       </c>
       <c r="CT10" t="n">
-        <v>0.000519127061124891</v>
+        <v>0.003454873338341713</v>
       </c>
       <c r="CU10" t="n">
-        <v>0.0001465051318518817</v>
+        <v>0.006883031688630581</v>
       </c>
       <c r="CV10" t="n">
-        <v>4.779230584972538e-05</v>
+        <v>0.01057044602930546</v>
       </c>
       <c r="CW10" t="n">
-        <v>0.0005235336720943451</v>
+        <v>0.01339286472648382</v>
       </c>
       <c r="CX10" t="n">
-        <v>0.0002475979854352772</v>
+        <v>0.01056359615176916</v>
       </c>
       <c r="CY10" t="n">
-        <v>0.0005926906014792621</v>
+        <v>0.005357545334845781</v>
       </c>
       <c r="CZ10" t="n">
-        <v>0.0001489756541559473</v>
+        <v>0.005998383741825819</v>
       </c>
       <c r="DA10" t="n">
-        <v>0.0005191586678847671</v>
+        <v>0.02246605418622494</v>
       </c>
       <c r="DB10" t="n">
-        <v>0.0002607469505164772</v>
+        <v>0.00257856328971684</v>
       </c>
       <c r="DC10" t="n">
-        <v>0.00034335270174779</v>
+        <v>0.008195015601813793</v>
       </c>
       <c r="DD10" t="n">
-        <v>0.0001146711510955356</v>
+        <v>0.007894418202340603</v>
       </c>
       <c r="DE10" t="n">
-        <v>0.0002754595188889652</v>
+        <v>0.02587795257568359</v>
       </c>
       <c r="DF10" t="n">
-        <v>0.00119916838593781</v>
+        <v>0.02263647690415382</v>
       </c>
       <c r="DG10" t="n">
-        <v>0.0001492756273364648</v>
+        <v>0.0400548055768013</v>
       </c>
       <c r="DH10" t="n">
-        <v>0.001043174299411476</v>
+        <v>0.03976508229970932</v>
       </c>
       <c r="DI10" t="n">
-        <v>0.0002036827645497397</v>
+        <v>0.04874539747834206</v>
       </c>
       <c r="DJ10" t="n">
-        <v>0.0001341928145848215</v>
+        <v>0.01804445683956146</v>
       </c>
       <c r="DK10" t="n">
-        <v>0.0007909850683063269</v>
+        <v>0.03207360953092575</v>
       </c>
       <c r="DL10" t="n">
-        <v>0.0007833083509467542</v>
+        <v>0.01575967483222485</v>
       </c>
       <c r="DM10" t="n">
-        <v>0.0004135882190894336</v>
+        <v>0.005446530878543854</v>
       </c>
       <c r="DN10" t="n">
-        <v>0.0002913306234404445</v>
+        <v>0.01860646530985832</v>
       </c>
       <c r="DO10" t="n">
-        <v>0.0003582238568924367</v>
+        <v>0.02894255518913269</v>
       </c>
       <c r="DP10" t="n">
-        <v>0.0004414330469444394</v>
+        <v>0.0007601100951433182</v>
       </c>
       <c r="DQ10" t="n">
-        <v>0.0006231306469999254</v>
+        <v>0.03445357829332352</v>
       </c>
       <c r="DR10" t="n">
-        <v>4.78833717352245e-05</v>
+        <v>0.03457764908671379</v>
       </c>
       <c r="DS10" t="n">
-        <v>6.145602674223483e-05</v>
+        <v>0.01074429787695408</v>
       </c>
       <c r="DT10" t="n">
-        <v>4.208366954117082e-05</v>
+        <v>0.006196692585945129</v>
       </c>
       <c r="DU10" t="n">
-        <v>9.512847464065999e-05</v>
+        <v>0.0487060584127903</v>
       </c>
       <c r="DV10" t="n">
-        <v>0.0002852985635399818</v>
+        <v>0.003934488631784916</v>
       </c>
       <c r="DW10" t="n">
-        <v>5.497300298884511e-05</v>
+        <v>0.02941517345607281</v>
       </c>
       <c r="DX10" t="n">
-        <v>6.032748206052929e-05</v>
+        <v>0.01584427244961262</v>
       </c>
       <c r="DY10" t="n">
-        <v>0.0003013024688698351</v>
+        <v>0.02117625810205936</v>
       </c>
       <c r="DZ10" t="n">
-        <v>3.688452125061303e-05</v>
+        <v>0.0008492707274854183</v>
       </c>
       <c r="EA10" t="n">
-        <v>0.000103845028206706</v>
+        <v>0.002327945549041033</v>
       </c>
       <c r="EB10" t="n">
-        <v>0.0002243412018287927</v>
+        <v>0.0269167572259903</v>
       </c>
       <c r="EC10" t="n">
-        <v>7.232128700707108e-05</v>
+        <v>0.003401349298655987</v>
       </c>
       <c r="ED10" t="n">
-        <v>7.397886656690389e-05</v>
+        <v>0.00781581923365593</v>
       </c>
       <c r="EE10" t="n">
-        <v>0.0002984414750244468</v>
+        <v>0.01611637696623802</v>
       </c>
       <c r="EF10" t="n">
-        <v>0.0001745953195495531</v>
+        <v>0.006709561683237553</v>
       </c>
       <c r="EG10" t="n">
-        <v>0.0002138932031812146</v>
+        <v>0.01322287134826183</v>
       </c>
       <c r="EH10" t="n">
-        <v>4.951035953126848e-05</v>
+        <v>0.007998472079634666</v>
       </c>
       <c r="EI10" t="n">
-        <v>0.0001626324228709564</v>
+        <v>0.01756997965276241</v>
       </c>
       <c r="EJ10" t="n">
-        <v>0.0001512668677605689</v>
+        <v>0.008993867784738541</v>
       </c>
       <c r="EK10" t="n">
-        <v>0.0004175609210506082</v>
+        <v>0.02402213029563427</v>
       </c>
       <c r="EL10" t="n">
-        <v>0.0003056106506846845</v>
+        <v>0.004771380219608545</v>
       </c>
       <c r="EM10" t="n">
-        <v>9.829772170633078e-05</v>
+        <v>0.01438692305237055</v>
       </c>
       <c r="EN10" t="n">
-        <v>0.0001615532382857054</v>
+        <v>0.008201242424547672</v>
       </c>
       <c r="EO10" t="n">
-        <v>0.0002862208057194948</v>
+        <v>0.004809591919183731</v>
       </c>
       <c r="EP10" t="n">
-        <v>0.0001874473091447726</v>
+        <v>0.006426163949072361</v>
       </c>
       <c r="EQ10" t="n">
-        <v>0.0001738429418765008</v>
+        <v>0.009048382751643658</v>
       </c>
       <c r="ER10" t="n">
-        <v>0.0002685307408683002</v>
+        <v>0.02217799425125122</v>
       </c>
       <c r="ES10" t="n">
-        <v>0.0002255287836305797</v>
+        <v>0.002258503576740623</v>
       </c>
       <c r="ET10" t="n">
-        <v>0.0006983275525271893</v>
+        <v>0.007987761870026588</v>
       </c>
       <c r="EU10" t="n">
-        <v>0.0002513341314624995</v>
+        <v>0.009461350739002228</v>
       </c>
       <c r="EV10" t="n">
-        <v>0.0005173356621526182</v>
+        <v>0.005157512612640858</v>
       </c>
       <c r="EW10" t="n">
-        <v>1.998383595491759e-05</v>
+        <v>0.01082474458962679</v>
       </c>
       <c r="EX10" t="n">
-        <v>7.216902304207906e-05</v>
+        <v>0.01389111578464508</v>
       </c>
       <c r="EY10" t="n">
-        <v>0.000485931639559567</v>
+        <v>0.01817530393600464</v>
       </c>
       <c r="EZ10" t="n">
-        <v>0.0001452969299862161</v>
+        <v>0.01309250853955746</v>
       </c>
       <c r="FA10" t="n">
-        <v>0.0003975777071900666</v>
+        <v>0.0004266448377165943</v>
       </c>
       <c r="FB10" t="n">
-        <v>0.0001518618810223415</v>
+        <v>0.007102289237082005</v>
       </c>
       <c r="FC10" t="n">
-        <v>0.0005122433649376035</v>
+        <v>0.02445349842309952</v>
       </c>
       <c r="FD10" t="n">
-        <v>0.0002944866428151727</v>
+        <v>0.01205363590270281</v>
       </c>
       <c r="FE10" t="n">
-        <v>7.670938066439703e-05</v>
+        <v>0.0001483712112531066</v>
       </c>
       <c r="FF10" t="n">
-        <v>0.0002595475525595248</v>
+        <v>0.007488544564694166</v>
       </c>
       <c r="FG10" t="n">
-        <v>0.0002107636537402868</v>
+        <v>0.02194341085851192</v>
       </c>
       <c r="FH10" t="n">
-        <v>0.0003886354097630829</v>
+        <v>0.003786810440942645</v>
       </c>
       <c r="FI10" t="n">
-        <v>0.0002129164786310866</v>
+        <v>0.003943126648664474</v>
       </c>
       <c r="FJ10" t="n">
-        <v>0.0002578881976660341</v>
+        <v>0.02415416575968266</v>
       </c>
       <c r="FK10" t="n">
-        <v>0.0001483218802604824</v>
+        <v>0.007319283671677113</v>
       </c>
       <c r="FL10" t="n">
-        <v>0.0001243357692146674</v>
+        <v>0.002362373284995556</v>
       </c>
       <c r="FM10" t="n">
-        <v>5.657807923853397e-05</v>
+        <v>0.0212795939296484</v>
       </c>
       <c r="FN10" t="n">
-        <v>7.971017475938424e-05</v>
+        <v>0.03110057674348354</v>
       </c>
       <c r="FO10" t="n">
-        <v>7.684493175474927e-05</v>
+        <v>0.009702463634312153</v>
       </c>
       <c r="FP10" t="n">
-        <v>0.0003894041874445975</v>
+        <v>0.01000836864113808</v>
       </c>
       <c r="FQ10" t="n">
-        <v>0.0001278280251426622</v>
+        <v>0.04277069866657257</v>
       </c>
       <c r="FR10" t="n">
-        <v>4.91371683892794e-05</v>
+        <v>0.0216322299093008</v>
       </c>
       <c r="FS10" t="n">
-        <v>0.0003756641817744821</v>
+        <v>0.02408947795629501</v>
       </c>
       <c r="FT10" t="n">
-        <v>0.001548519590869546</v>
+        <v>0.01786105334758759</v>
       </c>
       <c r="FU10" t="n">
-        <v>0.0003704233677126467</v>
+        <v>0.02550881914794445</v>
       </c>
       <c r="FV10" t="n">
-        <v>0.0001750358933350071</v>
+        <v>0.02738267928361893</v>
       </c>
       <c r="FW10" t="n">
-        <v>0.0004871929413639009</v>
+        <v>0.008927969262003899</v>
       </c>
       <c r="FX10" t="n">
-        <v>9.354714711662382e-05</v>
+        <v>0.01873522438108921</v>
       </c>
       <c r="FY10" t="n">
-        <v>0.0004175776266492903</v>
+        <v>0.007247497327625751</v>
       </c>
       <c r="FZ10" t="n">
-        <v>0.0004009910335298628</v>
+        <v>0.02031967975199223</v>
       </c>
       <c r="GA10" t="n">
-        <v>3.827709952020086e-05</v>
+        <v>0.002790327183902264</v>
       </c>
       <c r="GB10" t="n">
-        <v>0.0005152195226401091</v>
+        <v>0.01460337266325951</v>
       </c>
       <c r="GC10" t="n">
-        <v>0.0002328344562556595</v>
+        <v>0.01806374453008175</v>
       </c>
       <c r="GD10" t="n">
-        <v>0.0003741009277291596</v>
+        <v>0.000615636701695621</v>
       </c>
       <c r="GE10" t="n">
-        <v>0.00116399850230664</v>
+        <v>0.006448299624025822</v>
       </c>
       <c r="GF10" t="n">
-        <v>0.000547956267837435</v>
+        <v>0.008805951103568077</v>
       </c>
       <c r="GG10" t="n">
-        <v>0.0004109058936592191</v>
+        <v>0.02104090712964535</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>0.001070183236151934</v>
+        <v>3.064272732444806e-06</v>
       </c>
       <c r="B11" t="n">
-        <v>0.0005242241895757616</v>
+        <v>6.250986916711554e-05</v>
       </c>
       <c r="C11" t="n">
-        <v>0.002682355465367436</v>
+        <v>0.0001050735445460305</v>
       </c>
       <c r="D11" t="n">
-        <v>0.002169081708416343</v>
+        <v>0.0001358952140435576</v>
       </c>
       <c r="E11" t="n">
-        <v>0.001418792875483632</v>
+        <v>2.275431688758545e-05</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0005740289343520999</v>
+        <v>5.132637306815013e-05</v>
       </c>
       <c r="G11" t="n">
-        <v>0.0005921581177972257</v>
+        <v>2.928323920059483e-05</v>
       </c>
       <c r="H11" t="n">
-        <v>0.0003173980803694576</v>
+        <v>4.636339508579113e-05</v>
       </c>
       <c r="I11" t="n">
-        <v>0.0005317417089827359</v>
+        <v>9.072011744137853e-05</v>
       </c>
       <c r="J11" t="n">
-        <v>0.0008868294535204768</v>
+        <v>1.967424213944469e-05</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0005035190843045712</v>
+        <v>6.69896398903802e-05</v>
       </c>
       <c r="L11" t="n">
-        <v>0.002056797035038471</v>
+        <v>0.0001432348362868652</v>
       </c>
       <c r="M11" t="n">
-        <v>0.002275720005854964</v>
+        <v>0.0001777704455889761</v>
       </c>
       <c r="N11" t="n">
-        <v>5.615689588012174e-05</v>
+        <v>2.935770135081839e-05</v>
       </c>
       <c r="O11" t="n">
-        <v>0.0006294577615335584</v>
+        <v>7.641527918167412e-05</v>
       </c>
       <c r="P11" t="n">
-        <v>0.0003370787017047405</v>
+        <v>2.52470636041835e-06</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.25014620507136e-05</v>
+        <v>9.57212396315299e-05</v>
       </c>
       <c r="R11" t="n">
-        <v>0.0009769813623279333</v>
+        <v>5.232715921010822e-05</v>
       </c>
       <c r="S11" t="n">
-        <v>0.0003254271578043699</v>
+        <v>1.750049523252528e-05</v>
       </c>
       <c r="T11" t="n">
-        <v>0.0004239756963215768</v>
+        <v>1.677927684795577e-06</v>
       </c>
       <c r="U11" t="n">
-        <v>0.0004135834751650691</v>
+        <v>2.308803959749639e-05</v>
       </c>
       <c r="V11" t="n">
-        <v>0.0004531383456196636</v>
+        <v>2.035575380432419e-05</v>
       </c>
       <c r="W11" t="n">
-        <v>0.0003475963312666863</v>
+        <v>2.89886102109449e-05</v>
       </c>
       <c r="X11" t="n">
-        <v>0.0001731461670715362</v>
+        <v>3.722476685652509e-05</v>
       </c>
       <c r="Y11" t="n">
-        <v>0.0003700978995766491</v>
+        <v>1.975683335331269e-05</v>
       </c>
       <c r="Z11" t="n">
-        <v>0.0002574885438662022</v>
+        <v>1.046416582539678e-05</v>
       </c>
       <c r="AA11" t="n">
-        <v>4.045624518766999e-05</v>
+        <v>3.300313983345404e-05</v>
       </c>
       <c r="AB11" t="n">
-        <v>0.0008794124587439001</v>
+        <v>2.337867044843733e-05</v>
       </c>
       <c r="AC11" t="n">
-        <v>6.927968934178352e-05</v>
+        <v>9.259131729777437e-06</v>
       </c>
       <c r="AD11" t="n">
-        <v>9.643657540436834e-05</v>
+        <v>9.450022844248451e-06</v>
       </c>
       <c r="AE11" t="n">
-        <v>0.0009182635694742203</v>
+        <v>6.076493446016684e-05</v>
       </c>
       <c r="AF11" t="n">
-        <v>0.0007593284244649112</v>
+        <v>2.146347833331674e-05</v>
       </c>
       <c r="AG11" t="n">
-        <v>3.352655767230317e-06</v>
+        <v>2.713189132919069e-06</v>
       </c>
       <c r="AH11" t="n">
-        <v>4.335808625910431e-05</v>
+        <v>6.055239282432012e-06</v>
       </c>
       <c r="AI11" t="n">
-        <v>0.0003171199641656131</v>
+        <v>4.169986277702264e-05</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0.000360210775397718</v>
+        <v>2.189804035879206e-05</v>
       </c>
       <c r="AK11" t="n">
-        <v>0.0002627731009852141</v>
+        <v>7.439700311806519e-06</v>
       </c>
       <c r="AL11" t="n">
-        <v>4.687078762799501e-05</v>
+        <v>2.805037183861714e-06</v>
       </c>
       <c r="AM11" t="n">
-        <v>2.150512591470033e-05</v>
+        <v>2.649314774316736e-05</v>
       </c>
       <c r="AN11" t="n">
-        <v>0.0001670619240030646</v>
+        <v>3.19922219205182e-05</v>
       </c>
       <c r="AO11" t="n">
-        <v>0.0006517691072076559</v>
+        <v>3.410721183172427e-05</v>
       </c>
       <c r="AP11" t="n">
-        <v>0.0001562025572638959</v>
+        <v>5.502122803591192e-06</v>
       </c>
       <c r="AQ11" t="n">
-        <v>0.0002959671546705067</v>
+        <v>2.582611705292948e-05</v>
       </c>
       <c r="AR11" t="n">
-        <v>7.092978921718895e-05</v>
+        <v>2.620771192596294e-05</v>
       </c>
       <c r="AS11" t="n">
-        <v>0.0001990087330341339</v>
+        <v>3.99879427277483e-05</v>
       </c>
       <c r="AT11" t="n">
-        <v>0.0008846773416735232</v>
+        <v>2.270151526317932e-05</v>
       </c>
       <c r="AU11" t="n">
-        <v>0.0009676560875959694</v>
+        <v>4.592475306708366e-07</v>
       </c>
       <c r="AV11" t="n">
-        <v>0.001500040758401155</v>
+        <v>0.0001509800058556721</v>
       </c>
       <c r="AW11" t="n">
-        <v>0.001869140774942935</v>
+        <v>0.000105282713775523</v>
       </c>
       <c r="AX11" t="n">
-        <v>0.0003433837846387178</v>
+        <v>8.342304681718815e-06</v>
       </c>
       <c r="AY11" t="n">
-        <v>0.000686434970702976</v>
+        <v>7.996799831744283e-05</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.0004373713163658977</v>
+        <v>7.246168388519436e-05</v>
       </c>
       <c r="BA11" t="n">
-        <v>0.0005069856415502727</v>
+        <v>2.40375902649248e-05</v>
       </c>
       <c r="BB11" t="n">
-        <v>0.0004045004025101662</v>
+        <v>7.154539343900979e-05</v>
       </c>
       <c r="BC11" t="n">
-        <v>0.0007965218974277377</v>
+        <v>2.025055073318072e-05</v>
       </c>
       <c r="BD11" t="n">
-        <v>0.001543106860481203</v>
+        <v>1.499587415310089e-05</v>
       </c>
       <c r="BE11" t="n">
-        <v>0.0003453704121056944</v>
+        <v>2.556304025347345e-05</v>
       </c>
       <c r="BF11" t="n">
-        <v>0.0007806475041434169</v>
+        <v>1.718144994811155e-05</v>
       </c>
       <c r="BG11" t="n">
-        <v>0.0006162742502056062</v>
+        <v>1.367225468129618e-05</v>
       </c>
       <c r="BH11" t="n">
-        <v>0.001003530924208462</v>
+        <v>2.653880073921755e-05</v>
       </c>
       <c r="BI11" t="n">
-        <v>0.0006337865488603711</v>
+        <v>5.897433584323153e-05</v>
       </c>
       <c r="BJ11" t="n">
-        <v>7.83940777182579e-07</v>
+        <v>5.789082570117898e-05</v>
       </c>
       <c r="BK11" t="n">
-        <v>0.0008492241031490266</v>
+        <v>4.756102498504333e-05</v>
       </c>
       <c r="BL11" t="n">
-        <v>4.008491669083014e-05</v>
+        <v>4.454788358998485e-05</v>
       </c>
       <c r="BM11" t="n">
-        <v>0.0005365857505239546</v>
+        <v>3.929366357624531e-05</v>
       </c>
       <c r="BN11" t="n">
-        <v>0.000208970857784152</v>
+        <v>1.209423498949036e-05</v>
       </c>
       <c r="BO11" t="n">
-        <v>3.969223689637147e-05</v>
+        <v>2.530615347495768e-05</v>
       </c>
       <c r="BP11" t="n">
-        <v>0.0005491788615472615</v>
+        <v>3.285471393610351e-05</v>
       </c>
       <c r="BQ11" t="n">
-        <v>7.463518704753369e-05</v>
+        <v>1.139606411015848e-05</v>
       </c>
       <c r="BR11" t="n">
-        <v>2.272996061947197e-05</v>
+        <v>1.499720110587077e-05</v>
       </c>
       <c r="BS11" t="n">
-        <v>0.0002855139318853617</v>
+        <v>6.739336822647601e-05</v>
       </c>
       <c r="BT11" t="n">
-        <v>0.0002031073527177796</v>
+        <v>1.271114615519764e-05</v>
       </c>
       <c r="BU11" t="n">
-        <v>0.000238328633713536</v>
+        <v>1.546909516036976e-06</v>
       </c>
       <c r="BV11" t="n">
-        <v>0.0005807155393995345</v>
+        <v>2.78476181847509e-05</v>
       </c>
       <c r="BW11" t="n">
-        <v>0.00103259552270174</v>
+        <v>8.317852189065889e-05</v>
       </c>
       <c r="BX11" t="n">
-        <v>0.001248363638296723</v>
+        <v>9.980591130442917e-05</v>
       </c>
       <c r="BY11" t="n">
-        <v>0.0004832896811421961</v>
+        <v>8.210013220377732e-06</v>
       </c>
       <c r="BZ11" t="n">
-        <v>0.0002305278612766415</v>
+        <v>3.034313340322115e-05</v>
       </c>
       <c r="CA11" t="n">
-        <v>0.0001171511685242876</v>
+        <v>1.948445424204692e-05</v>
       </c>
       <c r="CB11" t="n">
-        <v>0.000376773503376171</v>
+        <v>2.34263607126195e-05</v>
       </c>
       <c r="CC11" t="n">
-        <v>0.0004659165279008448</v>
+        <v>4.057673504576087e-05</v>
       </c>
       <c r="CD11" t="n">
-        <v>0.0003178826882503927</v>
+        <v>1.178261072709574e-06</v>
       </c>
       <c r="CE11" t="n">
-        <v>6.014472091919743e-05</v>
+        <v>1.465675632061902e-05</v>
       </c>
       <c r="CF11" t="n">
-        <v>0.0007004234939813614</v>
+        <v>3.709683733177371e-05</v>
       </c>
       <c r="CG11" t="n">
-        <v>0.0003655343316495419</v>
+        <v>5.303511716192588e-05</v>
       </c>
       <c r="CH11" t="n">
-        <v>0.0003351240884512663</v>
+        <v>1.537719799671322e-05</v>
       </c>
       <c r="CI11" t="n">
-        <v>4.984392944606952e-05</v>
+        <v>1.775076270860154e-05</v>
       </c>
       <c r="CJ11" t="n">
-        <v>0.0002352340234210715</v>
+        <v>2.777172994683497e-06</v>
       </c>
       <c r="CK11" t="n">
-        <v>0.0001768205547705293</v>
+        <v>6.006327566865366e-06</v>
       </c>
       <c r="CL11" t="n">
-        <v>6.132340058684349e-05</v>
+        <v>1.024621633405332e-05</v>
       </c>
       <c r="CM11" t="n">
-        <v>0.0009825477609410882</v>
+        <v>1.759863152983598e-06</v>
       </c>
       <c r="CN11" t="n">
-        <v>0.0008236478315666318</v>
+        <v>1.608836646482814e-05</v>
       </c>
       <c r="CO11" t="n">
-        <v>1.780633465386927e-05</v>
+        <v>6.082762774894945e-05</v>
       </c>
       <c r="CP11" t="n">
-        <v>0.0003929930098820478</v>
+        <v>9.478766878601164e-05</v>
       </c>
       <c r="CQ11" t="n">
-        <v>0.0002285032824147493</v>
+        <v>2.571220102254301e-05</v>
       </c>
       <c r="CR11" t="n">
-        <v>0.000305788271361962</v>
+        <v>5.695691652363166e-05</v>
       </c>
       <c r="CS11" t="n">
-        <v>0.000214299390790984</v>
+        <v>4.617720151145477e-06</v>
       </c>
       <c r="CT11" t="n">
-        <v>0.001059880945831537</v>
+        <v>8.08096410764847e-06</v>
       </c>
       <c r="CU11" t="n">
-        <v>0.0002232005790574476</v>
+        <v>3.542286503943615e-05</v>
       </c>
       <c r="CV11" t="n">
-        <v>0.0002394314069533721</v>
+        <v>5.346458237909246e-06</v>
       </c>
       <c r="CW11" t="n">
-        <v>0.000229482728173025</v>
+        <v>2.689532084332313e-05</v>
       </c>
       <c r="CX11" t="n">
-        <v>0.0004642331041395664</v>
+        <v>3.178373663104139e-05</v>
       </c>
       <c r="CY11" t="n">
-        <v>0.000405839120503515</v>
+        <v>4.66819983557798e-05</v>
       </c>
       <c r="CZ11" t="n">
-        <v>0.0001458048791391775</v>
+        <v>1.506243552285014e-05</v>
       </c>
       <c r="DA11" t="n">
-        <v>2.162644886993803e-05</v>
+        <v>2.897980994021054e-05</v>
       </c>
       <c r="DB11" t="n">
-        <v>0.0002105302119161934</v>
+        <v>3.820943675236776e-06</v>
       </c>
       <c r="DC11" t="n">
-        <v>0.0001142617402365431</v>
+        <v>7.83535506343469e-06</v>
       </c>
       <c r="DD11" t="n">
-        <v>1.551390232634731e-05</v>
+        <v>1.222420814883662e-05</v>
       </c>
       <c r="DE11" t="n">
-        <v>8.069344039540738e-05</v>
+        <v>4.098566932952963e-05</v>
       </c>
       <c r="DF11" t="n">
-        <v>0.0009107223595492542</v>
+        <v>3.93508598790504e-05</v>
       </c>
       <c r="DG11" t="n">
-        <v>0.000819950713776052</v>
+        <v>1.619207523617661e-06</v>
       </c>
       <c r="DH11" t="n">
-        <v>0.0002655238495208323</v>
+        <v>2.522789691283833e-05</v>
       </c>
       <c r="DI11" t="n">
-        <v>0.0001158177401521243</v>
+        <v>1.617865927983075e-05</v>
       </c>
       <c r="DJ11" t="n">
-        <v>0.0002451590844430029</v>
+        <v>6.380485501722433e-06</v>
       </c>
       <c r="DK11" t="n">
-        <v>0.0008671774412505329</v>
+        <v>4.280119901522994e-05</v>
       </c>
       <c r="DL11" t="n">
-        <v>0.0002516661770641804</v>
+        <v>5.548241097130813e-05</v>
       </c>
       <c r="DM11" t="n">
-        <v>0.000287227361695841</v>
+        <v>5.941576091572642e-05</v>
       </c>
       <c r="DN11" t="n">
-        <v>2.635354758240283e-05</v>
+        <v>2.886183438022272e-06</v>
       </c>
       <c r="DO11" t="n">
-        <v>0.0006005583563819528</v>
+        <v>1.645419433771167e-05</v>
       </c>
       <c r="DP11" t="n">
-        <v>0.0004657107638195157</v>
+        <v>1.603796226845589e-05</v>
       </c>
       <c r="DQ11" t="n">
-        <v>7.76882516220212e-05</v>
+        <v>1.320916908298386e-05</v>
       </c>
       <c r="DR11" t="n">
-        <v>0.0009208928095176816</v>
+        <v>4.026188980787992e-05</v>
       </c>
       <c r="DS11" t="n">
-        <v>0.000384739541914314</v>
+        <v>1.184330358228181e-05</v>
       </c>
       <c r="DT11" t="n">
-        <v>0.0003924164338968694</v>
+        <v>2.299741026945412e-05</v>
       </c>
       <c r="DU11" t="n">
-        <v>0.0001353481638943776</v>
+        <v>2.073518407996744e-05</v>
       </c>
       <c r="DV11" t="n">
-        <v>0.0006486767088063061</v>
+        <v>3.693005055538379e-05</v>
       </c>
       <c r="DW11" t="n">
-        <v>0.0001973928592633456</v>
+        <v>5.071273335488513e-05</v>
       </c>
       <c r="DX11" t="n">
-        <v>0.0008868408622220159</v>
+        <v>3.026269769179635e-05</v>
       </c>
       <c r="DY11" t="n">
-        <v>0.0002827206335496157</v>
+        <v>2.355071774218231e-05</v>
       </c>
       <c r="DZ11" t="n">
-        <v>0.00017662147001829</v>
+        <v>7.546991128037916e-06</v>
       </c>
       <c r="EA11" t="n">
-        <v>0.0004324231122154742</v>
+        <v>2.597574166429695e-05</v>
       </c>
       <c r="EB11" t="n">
-        <v>0.000594095850829035</v>
+        <v>2.583576497272588e-05</v>
       </c>
       <c r="EC11" t="n">
-        <v>3.5028402635362e-05</v>
+        <v>1.300418989558239e-05</v>
       </c>
       <c r="ED11" t="n">
-        <v>0.0001719928113743663</v>
+        <v>4.361866740509868e-05</v>
       </c>
       <c r="EE11" t="n">
-        <v>3.601855132728815e-05</v>
+        <v>2.003025110752787e-05</v>
       </c>
       <c r="EF11" t="n">
-        <v>2.699517244764138e-05</v>
+        <v>2.588302595540881e-05</v>
       </c>
       <c r="EG11" t="n">
-        <v>0.0003040713490918279</v>
+        <v>2.05183205252979e-05</v>
       </c>
       <c r="EH11" t="n">
-        <v>0.0007177659426815808</v>
+        <v>1.219030400534393e-05</v>
       </c>
       <c r="EI11" t="n">
-        <v>0.0008410761947743595</v>
+        <v>6.341701373457909e-05</v>
       </c>
       <c r="EJ11" t="n">
-        <v>1.045762383000692e-05</v>
+        <v>1.4337202628667e-05</v>
       </c>
       <c r="EK11" t="n">
-        <v>6.241200026124716e-06</v>
+        <v>2.997167030116543e-06</v>
       </c>
       <c r="EL11" t="n">
-        <v>0.000284853857010603</v>
+        <v>1.057297140505398e-06</v>
       </c>
       <c r="EM11" t="n">
-        <v>8.849102596286684e-05</v>
+        <v>9.050801281773602e-07</v>
       </c>
       <c r="EN11" t="n">
-        <v>0.0002963391889352351</v>
+        <v>4.278235792298801e-06</v>
       </c>
       <c r="EO11" t="n">
-        <v>2.541033609304577e-05</v>
+        <v>4.3983773139189e-06</v>
       </c>
       <c r="EP11" t="n">
-        <v>0.0005958336405456066</v>
+        <v>2.416154893580824e-05</v>
       </c>
       <c r="EQ11" t="n">
-        <v>0.0003070450620725751</v>
+        <v>1.214638450619532e-05</v>
       </c>
       <c r="ER11" t="n">
-        <v>0.0004067666013725102</v>
+        <v>3.63583312719129e-05</v>
       </c>
       <c r="ES11" t="n">
-        <v>0.0002109721972374246</v>
+        <v>1.427303141099401e-05</v>
       </c>
       <c r="ET11" t="n">
-        <v>9.774179488886148e-05</v>
+        <v>5.824453546665609e-05</v>
       </c>
       <c r="EU11" t="n">
-        <v>0.0003155407612212002</v>
+        <v>4.272375917935278e-06</v>
       </c>
       <c r="EV11" t="n">
-        <v>1.3315071555553e-05</v>
+        <v>3.776823723455891e-05</v>
       </c>
       <c r="EW11" t="n">
-        <v>0.0003410975623410195</v>
+        <v>7.261677637870889e-06</v>
       </c>
       <c r="EX11" t="n">
-        <v>0.000243998336372897</v>
+        <v>5.432148100226186e-07</v>
       </c>
       <c r="EY11" t="n">
-        <v>0.0002914717770181596</v>
+        <v>2.055114600807428e-05</v>
       </c>
       <c r="EZ11" t="n">
-        <v>0.0006130626425147057</v>
+        <v>3.642231240519322e-05</v>
       </c>
       <c r="FA11" t="n">
-        <v>0.0003907536738552153</v>
+        <v>6.351586489472538e-05</v>
       </c>
       <c r="FB11" t="n">
-        <v>0.0001977596548385918</v>
+        <v>1.405094008077867e-05</v>
       </c>
       <c r="FC11" t="n">
-        <v>8.900729881133884e-06</v>
+        <v>2.357304765610024e-05</v>
       </c>
       <c r="FD11" t="n">
-        <v>0.0001807493099477142</v>
+        <v>5.186601811146829e-06</v>
       </c>
       <c r="FE11" t="n">
-        <v>9.517658327240497e-05</v>
+        <v>2.17209762922721e-05</v>
       </c>
       <c r="FF11" t="n">
-        <v>0.0001608886668691412</v>
+        <v>1.45528138091322e-05</v>
       </c>
       <c r="FG11" t="n">
-        <v>9.298199438489974e-05</v>
+        <v>1.398306812916417e-05</v>
       </c>
       <c r="FH11" t="n">
-        <v>0.0004095019539818168</v>
+        <v>2.208485602750443e-05</v>
       </c>
       <c r="FI11" t="n">
-        <v>1.380120556859765e-05</v>
+        <v>8.013086699065752e-06</v>
       </c>
       <c r="FJ11" t="n">
-        <v>0.0004054601886309683</v>
+        <v>2.634986776683945e-05</v>
       </c>
       <c r="FK11" t="n">
-        <v>0.0002826677518896759</v>
+        <v>8.841501767165028e-06</v>
       </c>
       <c r="FL11" t="n">
-        <v>0.0003187778347637504</v>
+        <v>3.385278978385031e-05</v>
       </c>
       <c r="FM11" t="n">
-        <v>0.0001936134358402342</v>
+        <v>8.276451808342244e-06</v>
       </c>
       <c r="FN11" t="n">
-        <v>0.0004320171719882637</v>
+        <v>1.102314490708522e-05</v>
       </c>
       <c r="FO11" t="n">
-        <v>0.0002905826841015369</v>
+        <v>5.018142474000342e-06</v>
       </c>
       <c r="FP11" t="n">
-        <v>0.0004354143457021564</v>
+        <v>8.164264727383852e-05</v>
       </c>
       <c r="FQ11" t="n">
-        <v>0.0002307973627466708</v>
+        <v>1.836224691942334e-05</v>
       </c>
       <c r="FR11" t="n">
-        <v>0.0006244128453545272</v>
+        <v>2.812497041304596e-05</v>
       </c>
       <c r="FS11" t="n">
-        <v>5.568485357798636e-05</v>
+        <v>1.278006038774038e-05</v>
       </c>
       <c r="FT11" t="n">
-        <v>4.509325663093477e-05</v>
+        <v>7.352170359808952e-05</v>
       </c>
       <c r="FU11" t="n">
-        <v>0.0003437700506765395</v>
+        <v>2.865882379410323e-05</v>
       </c>
       <c r="FV11" t="n">
-        <v>0.0001237188844243065</v>
+        <v>2.626672358019277e-05</v>
       </c>
       <c r="FW11" t="n">
-        <v>0.000308311078697443</v>
+        <v>3.693263352033682e-05</v>
       </c>
       <c r="FX11" t="n">
-        <v>0.000107096871943213</v>
+        <v>1.858088035078254e-05</v>
       </c>
       <c r="FY11" t="n">
-        <v>0.000135502777993679</v>
+        <v>3.106497752014548e-05</v>
       </c>
       <c r="FZ11" t="n">
-        <v>0.0005420373636297882</v>
+        <v>2.308529656147584e-05</v>
       </c>
       <c r="GA11" t="n">
-        <v>9.501620661467314e-05</v>
+        <v>1.095524567062967e-05</v>
       </c>
       <c r="GB11" t="n">
-        <v>4.416062438394874e-06</v>
+        <v>6.206709804246202e-05</v>
       </c>
       <c r="GC11" t="n">
-        <v>0.0005632381653413177</v>
+        <v>1.388840155414073e-05</v>
       </c>
       <c r="GD11" t="n">
-        <v>0.0008309768163599074</v>
+        <v>3.829242268693633e-05</v>
       </c>
       <c r="GE11" t="n">
-        <v>0.0002630728995427489</v>
+        <v>8.581333531765267e-06</v>
       </c>
       <c r="GF11" t="n">
-        <v>0.0001499563513789326</v>
+        <v>2.458778544678353e-05</v>
       </c>
       <c r="GG11" t="n">
-        <v>2.216751818195917e-05</v>
+        <v>4.33377645094879e-05</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>5.99786017119186e-06</v>
+        <v>2.820008376147598e-06</v>
       </c>
       <c r="B12" t="n">
-        <v>0.0001210503105539829</v>
+        <v>1.501924452895764e-05</v>
       </c>
       <c r="C12" t="n">
-        <v>1.985249036806636e-05</v>
+        <v>2.000200311158551e-06</v>
       </c>
       <c r="D12" t="n">
-        <v>4.851119956583716e-05</v>
+        <v>5.65989194001304e-06</v>
       </c>
       <c r="E12" t="n">
-        <v>5.99705490458291e-05</v>
+        <v>6.623610261158319e-06</v>
       </c>
       <c r="F12" t="n">
-        <v>5.99590057390742e-05</v>
+        <v>1.551083187223412e-05</v>
       </c>
       <c r="G12" t="n">
-        <v>2.350299109821208e-05</v>
+        <v>3.45855914929416e-06</v>
       </c>
       <c r="H12" t="n">
-        <v>2.821531234076247e-05</v>
+        <v>1.946955853782129e-05</v>
       </c>
       <c r="I12" t="n">
-        <v>9.561234037391841e-06</v>
+        <v>2.114098833772005e-06</v>
       </c>
       <c r="J12" t="n">
-        <v>1.15713646664517e-05</v>
+        <v>6.891664270369802e-06</v>
       </c>
       <c r="K12" t="n">
-        <v>9.425223834114149e-05</v>
+        <v>2.192974898207467e-05</v>
       </c>
       <c r="L12" t="n">
-        <v>3.524062094584224e-06</v>
+        <v>1.878345074146637e-06</v>
       </c>
       <c r="M12" t="n">
-        <v>3.06061738228891e-05</v>
+        <v>1.162763328466099e-05</v>
       </c>
       <c r="N12" t="n">
-        <v>4.385720967547968e-05</v>
+        <v>1.095031439035665e-05</v>
       </c>
       <c r="O12" t="n">
-        <v>5.345715180737898e-05</v>
+        <v>1.451306707167532e-05</v>
       </c>
       <c r="P12" t="n">
-        <v>2.537144064262975e-05</v>
+        <v>6.08816162639414e-06</v>
       </c>
       <c r="Q12" t="n">
-        <v>4.556904968922026e-06</v>
+        <v>1.116858402383514e-05</v>
       </c>
       <c r="R12" t="n">
-        <v>8.909118150768336e-06</v>
+        <v>2.164533270843094e-06</v>
       </c>
       <c r="S12" t="n">
-        <v>8.957767363426683e-07</v>
+        <v>3.049495262530399e-06</v>
       </c>
       <c r="T12" t="n">
-        <v>1.708003583189566e-05</v>
+        <v>3.223383600925445e-06</v>
       </c>
       <c r="U12" t="n">
-        <v>2.826865511451615e-06</v>
+        <v>1.374986254631949e-06</v>
       </c>
       <c r="V12" t="n">
-        <v>2.217849578300957e-05</v>
+        <v>1.095440666176728e-06</v>
       </c>
       <c r="W12" t="n">
-        <v>1.722491288091987e-05</v>
+        <v>8.390696848437074e-08</v>
       </c>
       <c r="X12" t="n">
-        <v>1.863746183516923e-05</v>
+        <v>1.956051391971414e-06</v>
       </c>
       <c r="Y12" t="n">
-        <v>6.268486231419956e-06</v>
+        <v>4.076488949067425e-06</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.6638012311887e-05</v>
+        <v>6.140078312455444e-07</v>
       </c>
       <c r="AA12" t="n">
-        <v>9.982203664549161e-06</v>
+        <v>3.163972905895207e-06</v>
       </c>
       <c r="AB12" t="n">
-        <v>7.672882929909974e-06</v>
+        <v>6.660404324065894e-06</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.362447073915973e-05</v>
+        <v>3.639767328422749e-06</v>
       </c>
       <c r="AD12" t="n">
-        <v>2.1707692212658e-06</v>
+        <v>2.952680461021373e-06</v>
       </c>
       <c r="AE12" t="n">
-        <v>8.614036232756916e-06</v>
+        <v>2.760856432360015e-06</v>
       </c>
       <c r="AF12" t="n">
-        <v>1.512737071607262e-06</v>
+        <v>8.960117156675551e-06</v>
       </c>
       <c r="AG12" t="n">
-        <v>4.681379778048722e-06</v>
+        <v>2.963019824164803e-06</v>
       </c>
       <c r="AH12" t="n">
-        <v>9.081031748792157e-06</v>
+        <v>3.990094228356611e-07</v>
       </c>
       <c r="AI12" t="n">
-        <v>8.091428753687069e-06</v>
+        <v>4.92102208227152e-06</v>
       </c>
       <c r="AJ12" t="n">
-        <v>4.920727860735497e-06</v>
+        <v>2.534400891818223e-06</v>
       </c>
       <c r="AK12" t="n">
-        <v>1.245277962880209e-05</v>
+        <v>2.169974095522775e-06</v>
       </c>
       <c r="AL12" t="n">
-        <v>2.221997783635743e-05</v>
+        <v>9.726550160849001e-07</v>
       </c>
       <c r="AM12" t="n">
-        <v>2.563771886343602e-06</v>
+        <v>4.718174295703648e-07</v>
       </c>
       <c r="AN12" t="n">
-        <v>7.894257578300312e-06</v>
+        <v>1.018639181893377e-06</v>
       </c>
       <c r="AO12" t="n">
-        <v>3.859800017380621e-06</v>
+        <v>7.117372661014087e-06</v>
       </c>
       <c r="AP12" t="n">
-        <v>2.335721364943311e-05</v>
+        <v>4.387471562949941e-06</v>
       </c>
       <c r="AQ12" t="n">
-        <v>1.003376837616088e-06</v>
+        <v>4.240107955411077e-06</v>
       </c>
       <c r="AR12" t="n">
-        <v>1.099936980608618e-05</v>
+        <v>5.299601525621256e-06</v>
       </c>
       <c r="AS12" t="n">
-        <v>1.406978662998881e-05</v>
+        <v>4.133318725507706e-06</v>
       </c>
       <c r="AT12" t="n">
-        <v>7.337956049013883e-06</v>
+        <v>1.370254949506489e-06</v>
       </c>
       <c r="AU12" t="n">
-        <v>8.235047425841913e-05</v>
+        <v>2.512751598260365e-05</v>
       </c>
       <c r="AV12" t="n">
-        <v>1.251908088306664e-05</v>
+        <v>7.030394044704735e-08</v>
       </c>
       <c r="AW12" t="n">
-        <v>4.714693204732612e-06</v>
+        <v>2.686279913177714e-06</v>
       </c>
       <c r="AX12" t="n">
-        <v>2.00087160919793e-05</v>
+        <v>1.051206982083386e-05</v>
       </c>
       <c r="AY12" t="n">
-        <v>3.587641549529508e-05</v>
+        <v>1.492365845479071e-05</v>
       </c>
       <c r="AZ12" t="n">
-        <v>1.736048716338701e-06</v>
+        <v>1.622139734536177e-06</v>
       </c>
       <c r="BA12" t="n">
-        <v>1.80827992153354e-05</v>
+        <v>3.444735739321914e-06</v>
       </c>
       <c r="BB12" t="n">
-        <v>9.518105798633769e-06</v>
+        <v>7.449785698554479e-06</v>
       </c>
       <c r="BC12" t="n">
-        <v>6.679400485154474e-06</v>
+        <v>1.171397912003158e-06</v>
       </c>
       <c r="BD12" t="n">
-        <v>1.942867675097659e-05</v>
+        <v>1.8020318748313e-06</v>
       </c>
       <c r="BE12" t="n">
-        <v>2.146295082638972e-05</v>
+        <v>7.496131502193748e-07</v>
       </c>
       <c r="BF12" t="n">
-        <v>1.443008113710675e-05</v>
+        <v>2.085956793962396e-06</v>
       </c>
       <c r="BG12" t="n">
-        <v>4.419406468514353e-05</v>
+        <v>2.936648115792195e-06</v>
       </c>
       <c r="BH12" t="n">
-        <v>1.164966852229554e-05</v>
+        <v>7.481095849470876e-07</v>
       </c>
       <c r="BI12" t="n">
-        <v>1.768121910572518e-05</v>
+        <v>2.752242153292173e-06</v>
       </c>
       <c r="BJ12" t="n">
-        <v>1.925318065332249e-05</v>
+        <v>1.158948634838453e-05</v>
       </c>
       <c r="BK12" t="n">
-        <v>6.859113454993349e-06</v>
+        <v>1.615713244973449e-06</v>
       </c>
       <c r="BL12" t="n">
-        <v>1.097332824429031e-05</v>
+        <v>1.234632577507e-06</v>
       </c>
       <c r="BM12" t="n">
-        <v>2.879385465348605e-05</v>
+        <v>8.56266706250608e-06</v>
       </c>
       <c r="BN12" t="n">
-        <v>1.285343296331121e-05</v>
+        <v>2.599764684418915e-06</v>
       </c>
       <c r="BO12" t="n">
-        <v>7.834205462131649e-06</v>
+        <v>5.454072834254475e-06</v>
       </c>
       <c r="BP12" t="n">
-        <v>2.273137170050177e-06</v>
+        <v>9.764075912244152e-06</v>
       </c>
       <c r="BQ12" t="n">
-        <v>8.656017598696053e-06</v>
+        <v>3.596743681555381e-06</v>
       </c>
       <c r="BR12" t="n">
-        <v>4.705586434283759e-06</v>
+        <v>1.83980318979593e-06</v>
       </c>
       <c r="BS12" t="n">
-        <v>5.951725142949726e-06</v>
+        <v>2.654201125551481e-07</v>
       </c>
       <c r="BT12" t="n">
-        <v>9.168913493340369e-06</v>
+        <v>2.678479859241634e-06</v>
       </c>
       <c r="BU12" t="n">
-        <v>6.703675353492144e-06</v>
+        <v>4.881116183241829e-06</v>
       </c>
       <c r="BV12" t="n">
-        <v>5.076784873381257e-05</v>
+        <v>1.098684333555866e-05</v>
       </c>
       <c r="BW12" t="n">
-        <v>2.474816392350476e-05</v>
+        <v>7.020809107416426e-07</v>
       </c>
       <c r="BX12" t="n">
-        <v>1.113477264880203e-05</v>
+        <v>1.646340024308302e-06</v>
       </c>
       <c r="BY12" t="n">
-        <v>1.577339753566775e-05</v>
+        <v>1.465861032556859e-06</v>
       </c>
       <c r="BZ12" t="n">
-        <v>4.891796379524749e-06</v>
+        <v>3.10607310893829e-06</v>
       </c>
       <c r="CA12" t="n">
-        <v>6.764526915503666e-06</v>
+        <v>5.445352144306526e-06</v>
       </c>
       <c r="CB12" t="n">
-        <v>5.685876203642692e-06</v>
+        <v>3.101925813098205e-06</v>
       </c>
       <c r="CC12" t="n">
-        <v>1.051495837600669e-05</v>
+        <v>3.420341045057285e-06</v>
       </c>
       <c r="CD12" t="n">
-        <v>5.33011643710779e-08</v>
+        <v>7.07156118551211e-07</v>
       </c>
       <c r="CE12" t="n">
-        <v>1.869632615125738e-05</v>
+        <v>3.900501269527012e-06</v>
       </c>
       <c r="CF12" t="n">
-        <v>7.360177733062301e-06</v>
+        <v>6.291472232078377e-08</v>
       </c>
       <c r="CG12" t="n">
-        <v>8.03492366685532e-06</v>
+        <v>4.505932906795351e-07</v>
       </c>
       <c r="CH12" t="n">
-        <v>1.908392164295947e-07</v>
+        <v>5.045823854743503e-06</v>
       </c>
       <c r="CI12" t="n">
-        <v>1.136659011535812e-05</v>
+        <v>2.753663920884719e-06</v>
       </c>
       <c r="CJ12" t="n">
-        <v>4.879997050011298e-06</v>
+        <v>9.974911563404021e-07</v>
       </c>
       <c r="CK12" t="n">
-        <v>4.150319000473246e-06</v>
+        <v>1.102603619074216e-06</v>
       </c>
       <c r="CL12" t="n">
-        <v>5.830835107190069e-06</v>
+        <v>2.211531295870373e-07</v>
       </c>
       <c r="CM12" t="n">
-        <v>1.902221265481785e-05</v>
+        <v>3.388777713553282e-06</v>
       </c>
       <c r="CN12" t="n">
-        <v>7.190580618043896e-06</v>
+        <v>1.226491804118268e-05</v>
       </c>
       <c r="CO12" t="n">
-        <v>5.703848728444427e-06</v>
+        <v>3.491870756988646e-06</v>
       </c>
       <c r="CP12" t="n">
-        <v>6.001099791319575e-06</v>
+        <v>1.075182353815762e-06</v>
       </c>
       <c r="CQ12" t="n">
-        <v>1.190149032481713e-05</v>
+        <v>8.334308404300828e-06</v>
       </c>
       <c r="CR12" t="n">
-        <v>1.00989309430588e-05</v>
+        <v>2.072724782919977e-06</v>
       </c>
       <c r="CS12" t="n">
-        <v>2.205769851570949e-05</v>
+        <v>1.268221240025014e-06</v>
       </c>
       <c r="CT12" t="n">
-        <v>1.772862560756039e-05</v>
+        <v>2.176391035391134e-06</v>
       </c>
       <c r="CU12" t="n">
-        <v>1.520919568065437e-06</v>
+        <v>1.022293645291938e-06</v>
       </c>
       <c r="CV12" t="n">
-        <v>3.331754214741522e-07</v>
+        <v>3.727633384187357e-07</v>
       </c>
       <c r="CW12" t="n">
-        <v>1.57350477820728e-05</v>
+        <v>4.267047643224942e-06</v>
       </c>
       <c r="CX12" t="n">
-        <v>8.420531230513006e-06</v>
+        <v>7.348609187829425e-07</v>
       </c>
       <c r="CY12" t="n">
-        <v>1.27651946968399e-05</v>
+        <v>1.404047907271888e-06</v>
       </c>
       <c r="CZ12" t="n">
-        <v>1.852504283306189e-06</v>
+        <v>2.70377586275572e-06</v>
       </c>
       <c r="DA12" t="n">
-        <v>1.579371746629477e-05</v>
+        <v>3.274489245086443e-06</v>
       </c>
       <c r="DB12" t="n">
-        <v>3.112233571300749e-06</v>
+        <v>2.382241063969559e-06</v>
       </c>
       <c r="DC12" t="n">
-        <v>7.459331754944287e-06</v>
+        <v>2.511306433916616e-07</v>
       </c>
       <c r="DD12" t="n">
-        <v>1.462197133150767e-06</v>
+        <v>3.54954920567252e-07</v>
       </c>
       <c r="DE12" t="n">
-        <v>4.726956831291318e-06</v>
+        <v>2.321797865079134e-07</v>
       </c>
       <c r="DF12" t="n">
-        <v>2.462342126818839e-05</v>
+        <v>7.63554544391809e-06</v>
       </c>
       <c r="DG12" t="n">
-        <v>4.535534117167117e-06</v>
+        <v>5.890164175070822e-06</v>
       </c>
       <c r="DH12" t="n">
-        <v>3.206069231964648e-05</v>
+        <v>2.196413106503314e-06</v>
       </c>
       <c r="DI12" t="n">
-        <v>7.966709745232947e-06</v>
+        <v>3.075803078900208e-06</v>
       </c>
       <c r="DJ12" t="n">
-        <v>3.281285671619116e-06</v>
+        <v>7.269149136845954e-06</v>
       </c>
       <c r="DK12" t="n">
-        <v>1.93261839740444e-05</v>
+        <v>2.551528041294659e-06</v>
       </c>
       <c r="DL12" t="n">
-        <v>1.305141449847724e-05</v>
+        <v>3.896832822647411e-06</v>
       </c>
       <c r="DM12" t="n">
-        <v>1.177073045255383e-05</v>
+        <v>6.838100489403587e-06</v>
       </c>
       <c r="DN12" t="n">
-        <v>5.026999133406207e-06</v>
+        <v>4.047645916216425e-07</v>
       </c>
       <c r="DO12" t="n">
-        <v>7.914016350696329e-06</v>
+        <v>2.547336862335214e-06</v>
       </c>
       <c r="DP12" t="n">
-        <v>1.647102408242063e-06</v>
+        <v>2.035333750427526e-07</v>
       </c>
       <c r="DQ12" t="n">
-        <v>3.618323944465374e-06</v>
+        <v>8.276578228105791e-06</v>
       </c>
       <c r="DR12" t="n">
-        <v>2.525655872887e-06</v>
+        <v>1.091463445845875e-06</v>
       </c>
       <c r="DS12" t="n">
-        <v>1.193718890135642e-05</v>
+        <v>3.640914655989036e-06</v>
       </c>
       <c r="DT12" t="n">
-        <v>5.891160526516614e-06</v>
+        <v>1.100257577490993e-06</v>
       </c>
       <c r="DU12" t="n">
-        <v>7.634464054717682e-06</v>
+        <v>9.894781669572694e-07</v>
       </c>
       <c r="DV12" t="n">
-        <v>6.310720436886186e-06</v>
+        <v>4.945366526953876e-06</v>
       </c>
       <c r="DW12" t="n">
-        <v>3.048755843337858e-06</v>
+        <v>2.77803155768197e-06</v>
       </c>
       <c r="DX12" t="n">
-        <v>2.338362946829875e-06</v>
+        <v>2.613888455016422e-06</v>
       </c>
       <c r="DY12" t="n">
-        <v>1.289136616833275e-05</v>
+        <v>2.152309434677591e-06</v>
       </c>
       <c r="DZ12" t="n">
-        <v>1.322751586485538e-06</v>
+        <v>2.9435118449328e-06</v>
       </c>
       <c r="EA12" t="n">
-        <v>5.04848458149354e-06</v>
+        <v>9.960127499653026e-06</v>
       </c>
       <c r="EB12" t="n">
-        <v>4.525616532191634e-06</v>
+        <v>3.137220573989907e-06</v>
       </c>
       <c r="EC12" t="n">
-        <v>8.512369049640256e-07</v>
+        <v>6.319833687484788e-07</v>
       </c>
       <c r="ED12" t="n">
-        <v>8.572059414291289e-06</v>
+        <v>7.277817076101201e-06</v>
       </c>
       <c r="EE12" t="n">
-        <v>6.937707439647056e-07</v>
+        <v>4.850830464420142e-06</v>
       </c>
       <c r="EF12" t="n">
-        <v>5.773405973741319e-06</v>
+        <v>3.361204790053307e-07</v>
       </c>
       <c r="EG12" t="n">
-        <v>1.540171251690481e-05</v>
+        <v>4.297627640426072e-07</v>
       </c>
       <c r="EH12" t="n">
-        <v>9.544208296574652e-06</v>
+        <v>6.3246682202589e-07</v>
       </c>
       <c r="EI12" t="n">
-        <v>2.803829374897759e-06</v>
+        <v>1.059133774106158e-05</v>
       </c>
       <c r="EJ12" t="n">
-        <v>8.28500105853891e-06</v>
+        <v>4.775668571710412e-07</v>
       </c>
       <c r="EK12" t="n">
-        <v>8.511537089361809e-06</v>
+        <v>2.915665390901268e-06</v>
       </c>
       <c r="EL12" t="n">
-        <v>5.96288464294048e-06</v>
+        <v>4.492935659072828e-07</v>
       </c>
       <c r="EM12" t="n">
-        <v>2.707903831833391e-06</v>
+        <v>1.734794977892307e-06</v>
       </c>
       <c r="EN12" t="n">
-        <v>6.714560640830314e-08</v>
+        <v>3.041206468878954e-07</v>
       </c>
       <c r="EO12" t="n">
-        <v>5.163519745110534e-06</v>
+        <v>1.551955620016088e-06</v>
       </c>
       <c r="EP12" t="n">
-        <v>8.14022496342659e-06</v>
+        <v>1.045700514623604e-06</v>
       </c>
       <c r="EQ12" t="n">
-        <v>1.370988411508733e-05</v>
+        <v>1.149768650066108e-06</v>
       </c>
       <c r="ER12" t="n">
-        <v>1.606374280527234e-05</v>
+        <v>3.791531298702466e-06</v>
       </c>
       <c r="ES12" t="n">
-        <v>9.645586942497175e-06</v>
+        <v>4.326055204728618e-06</v>
       </c>
       <c r="ET12" t="n">
-        <v>1.535720366518945e-05</v>
+        <v>5.257423708826536e-06</v>
       </c>
       <c r="EU12" t="n">
-        <v>6.501652933366131e-06</v>
+        <v>3.670025080282358e-06</v>
       </c>
       <c r="EV12" t="n">
-        <v>1.951166268554516e-05</v>
+        <v>1.120768502005376e-06</v>
       </c>
       <c r="EW12" t="n">
-        <v>2.271710400236771e-06</v>
+        <v>1.556538791191997e-06</v>
       </c>
       <c r="EX12" t="n">
-        <v>1.790878741303459e-06</v>
+        <v>3.70524844583997e-07</v>
       </c>
       <c r="EY12" t="n">
-        <v>1.46308357216185e-05</v>
+        <v>4.847322088608053e-06</v>
       </c>
       <c r="EZ12" t="n">
-        <v>5.551692993321922e-06</v>
+        <v>3.261174867930094e-07</v>
       </c>
       <c r="FA12" t="n">
-        <v>1.215464271808742e-05</v>
+        <v>4.821288257517153e-07</v>
       </c>
       <c r="FB12" t="n">
-        <v>2.924494765466079e-06</v>
+        <v>3.833007212961093e-06</v>
       </c>
       <c r="FC12" t="n">
-        <v>1.222731953021139e-05</v>
+        <v>2.694489467103267e-06</v>
       </c>
       <c r="FD12" t="n">
-        <v>7.215533969429089e-06</v>
+        <v>6.720023293382837e-07</v>
       </c>
       <c r="FE12" t="n">
-        <v>6.210501851455774e-06</v>
+        <v>1.988077826808876e-07</v>
       </c>
       <c r="FF12" t="n">
-        <v>6.7107830545865e-06</v>
+        <v>9.005345305013179e-07</v>
       </c>
       <c r="FG12" t="n">
-        <v>6.739264790667221e-06</v>
+        <v>1.03980028143269e-06</v>
       </c>
       <c r="FH12" t="n">
-        <v>1.061777220456861e-05</v>
+        <v>2.31889248425432e-06</v>
       </c>
       <c r="FI12" t="n">
-        <v>8.46879538585199e-06</v>
+        <v>5.253381232250831e-07</v>
       </c>
       <c r="FJ12" t="n">
-        <v>1.66459667525487e-05</v>
+        <v>4.731484295916744e-06</v>
       </c>
       <c r="FK12" t="n">
-        <v>4.931749117531581e-06</v>
+        <v>4.40629310105578e-06</v>
       </c>
       <c r="FL12" t="n">
-        <v>9.084741577680688e-06</v>
+        <v>5.912025926591014e-07</v>
       </c>
       <c r="FM12" t="n">
-        <v>3.594415375118842e-06</v>
+        <v>2.14779720408842e-06</v>
       </c>
       <c r="FN12" t="n">
-        <v>8.135753887472674e-06</v>
+        <v>6.353175194817595e-07</v>
       </c>
       <c r="FO12" t="n">
-        <v>8.220767085731495e-06</v>
+        <v>8.28431893751258e-06</v>
       </c>
       <c r="FP12" t="n">
-        <v>2.534372470108792e-06</v>
+        <v>1.903517841128632e-07</v>
       </c>
       <c r="FQ12" t="n">
-        <v>4.386961336422246e-06</v>
+        <v>1.559872544021346e-06</v>
       </c>
       <c r="FR12" t="n">
-        <v>1.104487273551058e-05</v>
+        <v>2.927699824795127e-07</v>
       </c>
       <c r="FS12" t="n">
-        <v>1.957268614205532e-05</v>
+        <v>7.282102160388604e-06</v>
       </c>
       <c r="FT12" t="n">
-        <v>9.523603694105987e-06</v>
+        <v>9.90222815744346e-06</v>
       </c>
       <c r="FU12" t="n">
-        <v>1.945634039657307e-06</v>
+        <v>5.812241397507023e-06</v>
       </c>
       <c r="FV12" t="n">
-        <v>8.538063411833718e-06</v>
+        <v>9.544737622491084e-06</v>
       </c>
       <c r="FW12" t="n">
-        <v>6.747131919837557e-06</v>
+        <v>1.290506952500436e-05</v>
       </c>
       <c r="FX12" t="n">
-        <v>8.983845418697456e-07</v>
+        <v>3.934900632884819e-06</v>
       </c>
       <c r="FY12" t="n">
-        <v>2.253436468890868e-05</v>
+        <v>3.43157580573461e-06</v>
       </c>
       <c r="FZ12" t="n">
-        <v>8.484075806336477e-07</v>
+        <v>2.448884515615646e-06</v>
       </c>
       <c r="GA12" t="n">
-        <v>4.361500941740815e-06</v>
+        <v>2.975149300254998e-06</v>
       </c>
       <c r="GB12" t="n">
-        <v>1.153936864284333e-05</v>
+        <v>1.714841118882759e-06</v>
       </c>
       <c r="GC12" t="n">
-        <v>1.167244045063853e-05</v>
+        <v>1.792594730432029e-07</v>
       </c>
       <c r="GD12" t="n">
-        <v>1.639102265471593e-05</v>
+        <v>2.458803919580532e-06</v>
       </c>
       <c r="GE12" t="n">
-        <v>4.67333520646207e-05</v>
+        <v>4.75497745355824e-06</v>
       </c>
       <c r="GF12" t="n">
-        <v>5.13345639774343e-07</v>
+        <v>3.715263574122218e-06</v>
       </c>
       <c r="GG12" t="n">
-        <v>1.356988605039078e-06</v>
+        <v>2.708704016640695e-07</v>
       </c>
     </row>
   </sheetData>
